--- a/data/raw/ASML.xlsx
+++ b/data/raw/ASML.xlsx
@@ -468,5022 +468,5022 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45834</v>
+        <v>45845</v>
       </c>
       <c r="B2" t="n">
-        <v>791.8844604492188</v>
+        <v>778.9855346679688</v>
       </c>
       <c r="C2" t="n">
-        <v>794.6527449415751</v>
+        <v>787.3201838675226</v>
       </c>
       <c r="D2" t="n">
-        <v>780.3845521002864</v>
+        <v>777.7055263447587</v>
       </c>
       <c r="E2" t="n">
-        <v>793.5414583708429</v>
+        <v>779.3526528764896</v>
       </c>
       <c r="F2" t="n">
-        <v>1705800</v>
+        <v>1363700</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45835</v>
+        <v>45846</v>
       </c>
       <c r="B3" t="n">
-        <v>789.7611083984375</v>
+        <v>787.9254150390625</v>
       </c>
       <c r="C3" t="n">
-        <v>799.2269083926864</v>
+        <v>792.1820967073372</v>
       </c>
       <c r="D3" t="n">
-        <v>782.3194245965059</v>
+        <v>772.6749300193111</v>
       </c>
       <c r="E3" t="n">
-        <v>796.6967480121452</v>
+        <v>776.5743648579542</v>
       </c>
       <c r="F3" t="n">
-        <v>1201000</v>
+        <v>1327800</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45838</v>
+        <v>45847</v>
       </c>
       <c r="B4" t="n">
-        <v>795.1587524414062</v>
+        <v>793.6109008789062</v>
       </c>
       <c r="C4" t="n">
-        <v>796.2005759833454</v>
+        <v>794.6725883104557</v>
       </c>
       <c r="D4" t="n">
-        <v>787.8658665266853</v>
+        <v>786.3080828817439</v>
       </c>
       <c r="E4" t="n">
-        <v>790.286896564243</v>
+        <v>786.7446640633102</v>
       </c>
       <c r="F4" t="n">
-        <v>1080400</v>
+        <v>1334300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45839</v>
+        <v>45848</v>
       </c>
       <c r="B5" t="n">
-        <v>784.3236083984375</v>
+        <v>795.8533325195312</v>
       </c>
       <c r="C5" t="n">
-        <v>789.3145263013221</v>
+        <v>804.7932239068926</v>
       </c>
       <c r="D5" t="n">
-        <v>776.455276013199</v>
+        <v>791.7951078888368</v>
       </c>
       <c r="E5" t="n">
-        <v>781.9224422584158</v>
+        <v>802.6401138160854</v>
       </c>
       <c r="F5" t="n">
-        <v>1065800</v>
+        <v>1498900</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45840</v>
+        <v>45849</v>
       </c>
       <c r="B6" t="n">
-        <v>793.3727416992188</v>
+        <v>795.694580078125</v>
       </c>
       <c r="C6" t="n">
-        <v>794.2756392645981</v>
+        <v>796.9447926284849</v>
       </c>
       <c r="D6" t="n">
-        <v>766.8505420701315</v>
+        <v>790.3266722198488</v>
       </c>
       <c r="E6" t="n">
-        <v>770.2042654168065</v>
+        <v>790.8723835786598</v>
       </c>
       <c r="F6" t="n">
-        <v>1383000</v>
+        <v>932400</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45841</v>
+        <v>45852</v>
       </c>
       <c r="B7" t="n">
-        <v>788.3223876953125</v>
+        <v>800.4572143554688</v>
       </c>
       <c r="C7" t="n">
-        <v>792.3210816132415</v>
+        <v>806.4502888160928</v>
       </c>
       <c r="D7" t="n">
-        <v>780.4937216328742</v>
+        <v>783.7283245964145</v>
       </c>
       <c r="E7" t="n">
-        <v>780.8509079285055</v>
+        <v>791.4180641145248</v>
       </c>
       <c r="F7" t="n">
-        <v>910700</v>
+        <v>1456900</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45845</v>
+        <v>45853</v>
       </c>
       <c r="B8" t="n">
-        <v>778.9855346679688</v>
+        <v>816.62060546875</v>
       </c>
       <c r="C8" t="n">
-        <v>787.3201838675226</v>
+        <v>820.1330583027431</v>
       </c>
       <c r="D8" t="n">
-        <v>777.7055263447587</v>
+        <v>807.879110280608</v>
       </c>
       <c r="E8" t="n">
-        <v>779.3526528764896</v>
+        <v>816.5808777310459</v>
       </c>
       <c r="F8" t="n">
-        <v>1363700</v>
+        <v>2099600</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45846</v>
+        <v>45854</v>
       </c>
       <c r="B9" t="n">
-        <v>787.9254150390625</v>
+        <v>748.5836791992188</v>
       </c>
       <c r="C9" t="n">
-        <v>792.1820967073372</v>
+        <v>754.9835384220911</v>
       </c>
       <c r="D9" t="n">
-        <v>772.6749300193111</v>
+        <v>724.9190919184446</v>
       </c>
       <c r="E9" t="n">
-        <v>776.5743648579542</v>
+        <v>748.4943523603254</v>
       </c>
       <c r="F9" t="n">
-        <v>1327800</v>
+        <v>10789600</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45847</v>
+        <v>45855</v>
       </c>
       <c r="B10" t="n">
-        <v>793.6109008789062</v>
+        <v>739.117919921875</v>
       </c>
       <c r="C10" t="n">
-        <v>794.6725883104557</v>
+        <v>750.9650827825097</v>
       </c>
       <c r="D10" t="n">
-        <v>786.3080828817439</v>
+        <v>736.2305732958994</v>
       </c>
       <c r="E10" t="n">
-        <v>786.7446640633102</v>
+        <v>741.013102616115</v>
       </c>
       <c r="F10" t="n">
-        <v>1334300</v>
+        <v>4078500</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45848</v>
+        <v>45856</v>
       </c>
       <c r="B11" t="n">
-        <v>795.8533325195312</v>
+        <v>728.8682861328125</v>
       </c>
       <c r="C11" t="n">
-        <v>804.7932239068926</v>
+        <v>746.2421467213438</v>
       </c>
       <c r="D11" t="n">
-        <v>791.7951078888368</v>
+        <v>728.6202300091854</v>
       </c>
       <c r="E11" t="n">
-        <v>802.6401138160854</v>
+        <v>746.2322147867064</v>
       </c>
       <c r="F11" t="n">
-        <v>1498900</v>
+        <v>2567200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45849</v>
+        <v>45859</v>
       </c>
       <c r="B12" t="n">
-        <v>795.694580078125</v>
+        <v>714.0841064453125</v>
       </c>
       <c r="C12" t="n">
-        <v>796.9447926284849</v>
+        <v>727.2013455614235</v>
       </c>
       <c r="D12" t="n">
-        <v>790.3266722198488</v>
+        <v>713.7269201670777</v>
       </c>
       <c r="E12" t="n">
-        <v>790.8723835786598</v>
+        <v>725.3160948253351</v>
       </c>
       <c r="F12" t="n">
-        <v>932400</v>
+        <v>2650300</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45852</v>
+        <v>45860</v>
       </c>
       <c r="B13" t="n">
-        <v>800.4572143554688</v>
+        <v>699.9944458007812</v>
       </c>
       <c r="C13" t="n">
-        <v>806.4502888160928</v>
+        <v>713.4688700225064</v>
       </c>
       <c r="D13" t="n">
-        <v>783.7283245964145</v>
+        <v>695.7378249541447</v>
       </c>
       <c r="E13" t="n">
-        <v>791.4180641145248</v>
+        <v>712.7247017273243</v>
       </c>
       <c r="F13" t="n">
-        <v>1456900</v>
+        <v>3425100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45853</v>
+        <v>45861</v>
       </c>
       <c r="B14" t="n">
-        <v>816.6205444335938</v>
+        <v>711.3555297851562</v>
       </c>
       <c r="C14" t="n">
-        <v>820.1329970050621</v>
+        <v>714.3718705747294</v>
       </c>
       <c r="D14" t="n">
-        <v>807.879049898801</v>
+        <v>702.6239659748511</v>
       </c>
       <c r="E14" t="n">
-        <v>816.5808166988589</v>
+        <v>709.6489326512158</v>
       </c>
       <c r="F14" t="n">
-        <v>2099600</v>
+        <v>3379400</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45854</v>
+        <v>45862</v>
       </c>
       <c r="B15" t="n">
-        <v>748.583740234375</v>
+        <v>719.442138671875</v>
       </c>
       <c r="C15" t="n">
-        <v>754.9835999790547</v>
+        <v>720.9800744946886</v>
       </c>
       <c r="D15" t="n">
-        <v>724.9191510241282</v>
+        <v>712.774358714104</v>
       </c>
       <c r="E15" t="n">
-        <v>748.4944133881985</v>
+        <v>717.3882267431204</v>
       </c>
       <c r="F15" t="n">
-        <v>10789600</v>
+        <v>2037100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45855</v>
+        <v>45863</v>
       </c>
       <c r="B16" t="n">
-        <v>739.1178588867188</v>
+        <v>705.7196655273438</v>
       </c>
       <c r="C16" t="n">
-        <v>750.965020769034</v>
+        <v>707.6049162746</v>
       </c>
       <c r="D16" t="n">
-        <v>736.2305124991755</v>
+        <v>701.1057974441294</v>
       </c>
       <c r="E16" t="n">
-        <v>741.0130414244577</v>
+        <v>703.6260863968379</v>
       </c>
       <c r="F16" t="n">
-        <v>4078500</v>
+        <v>2312100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45856</v>
+        <v>45866</v>
       </c>
       <c r="B17" t="n">
-        <v>728.8682861328125</v>
+        <v>724.3139038085938</v>
       </c>
       <c r="C17" t="n">
-        <v>746.2421467213438</v>
+        <v>729.691743275914</v>
       </c>
       <c r="D17" t="n">
-        <v>728.6202300091854</v>
+        <v>722.8255671598076</v>
       </c>
       <c r="E17" t="n">
-        <v>746.2322147867064</v>
+        <v>729.4338157943392</v>
       </c>
       <c r="F17" t="n">
-        <v>2567200</v>
+        <v>2253900</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45859</v>
+        <v>45867</v>
       </c>
       <c r="B18" t="n">
-        <v>714.0841064453125</v>
+        <v>714.711669921875</v>
       </c>
       <c r="C18" t="n">
-        <v>727.2013455614235</v>
+        <v>723.0973318303609</v>
       </c>
       <c r="D18" t="n">
-        <v>713.7269201670777</v>
+        <v>711.9363635403377</v>
       </c>
       <c r="E18" t="n">
-        <v>725.3160948253351</v>
+        <v>718.9293633373032</v>
       </c>
       <c r="F18" t="n">
-        <v>2650300</v>
+        <v>2292900</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45860</v>
+        <v>45868</v>
       </c>
       <c r="B19" t="n">
-        <v>699.9945068359375</v>
+        <v>717.6561889648438</v>
       </c>
       <c r="C19" t="n">
-        <v>713.4689322325486</v>
+        <v>720.2126816264328</v>
       </c>
       <c r="D19" t="n">
-        <v>695.7378856181501</v>
+        <v>711.7374655432036</v>
       </c>
       <c r="E19" t="n">
-        <v>712.7247638724796</v>
+        <v>713.1201706486498</v>
       </c>
       <c r="F19" t="n">
-        <v>3425100</v>
+        <v>1407000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45861</v>
+        <v>45869</v>
       </c>
       <c r="B20" t="n">
-        <v>711.35546875</v>
+        <v>691.0567626953125</v>
       </c>
       <c r="C20" t="n">
-        <v>714.3718092807675</v>
+        <v>703.8192500875333</v>
       </c>
       <c r="D20" t="n">
-        <v>702.6239056888735</v>
+        <v>687.5751680832676</v>
       </c>
       <c r="E20" t="n">
-        <v>709.6488717624876</v>
+        <v>702.6852911281102</v>
       </c>
       <c r="F20" t="n">
-        <v>3379400</v>
+        <v>2892200</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45862</v>
+        <v>45870</v>
       </c>
       <c r="B21" t="n">
-        <v>719.4420776367188</v>
+        <v>686.1924438476562</v>
       </c>
       <c r="C21" t="n">
-        <v>720.9800133290588</v>
+        <v>689.7834453325968</v>
       </c>
       <c r="D21" t="n">
-        <v>712.7742982446207</v>
+        <v>679.8857573557855</v>
       </c>
       <c r="E21" t="n">
-        <v>717.3881658822114</v>
+        <v>686.3714899941258</v>
       </c>
       <c r="F21" t="n">
-        <v>2037100</v>
+        <v>1627100</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45863</v>
+        <v>45873</v>
       </c>
       <c r="B22" t="n">
-        <v>705.7196655273438</v>
+        <v>695.6822509765625</v>
       </c>
       <c r="C22" t="n">
-        <v>707.6049162746</v>
+        <v>695.7718044065165</v>
       </c>
       <c r="D22" t="n">
-        <v>701.1057974441294</v>
+        <v>689.2562611281992</v>
       </c>
       <c r="E22" t="n">
-        <v>703.6260863968379</v>
+        <v>691.9221604880988</v>
       </c>
       <c r="F22" t="n">
-        <v>2312100</v>
+        <v>1025600</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45866</v>
+        <v>45874</v>
       </c>
       <c r="B23" t="n">
-        <v>724.3139038085938</v>
+        <v>686.0034790039062</v>
       </c>
       <c r="C23" t="n">
-        <v>729.691743275914</v>
+        <v>691.9719270773378</v>
       </c>
       <c r="D23" t="n">
-        <v>722.8255671598076</v>
+        <v>680.6418085798671</v>
       </c>
       <c r="E23" t="n">
-        <v>729.4338157943392</v>
+        <v>691.0666784529191</v>
       </c>
       <c r="F23" t="n">
-        <v>2253900</v>
+        <v>1261200</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45867</v>
+        <v>45875</v>
       </c>
       <c r="B24" t="n">
-        <v>714.711669921875</v>
+        <v>687.3264770507812</v>
       </c>
       <c r="C24" t="n">
-        <v>723.0973318303609</v>
+        <v>688.7887176328952</v>
       </c>
       <c r="D24" t="n">
-        <v>711.9363635403377</v>
+        <v>681.8354855939474</v>
       </c>
       <c r="E24" t="n">
-        <v>718.9293633373032</v>
+        <v>684.0338857449923</v>
       </c>
       <c r="F24" t="n">
-        <v>2292900</v>
+        <v>1218700</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45868</v>
+        <v>45876</v>
       </c>
       <c r="B25" t="n">
-        <v>717.6561279296875</v>
+        <v>709.369873046875</v>
       </c>
       <c r="C25" t="n">
-        <v>720.2126203738521</v>
+        <v>713.1300241025148</v>
       </c>
       <c r="D25" t="n">
-        <v>711.7374050114223</v>
+        <v>702.9040549428026</v>
       </c>
       <c r="E25" t="n">
-        <v>713.1201099992725</v>
+        <v>710.2651644546523</v>
       </c>
       <c r="F25" t="n">
-        <v>1407000</v>
+        <v>1723800</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45869</v>
+        <v>45877</v>
       </c>
       <c r="B26" t="n">
-        <v>691.0567016601562</v>
+        <v>718.5215454101562</v>
       </c>
       <c r="C26" t="n">
-        <v>703.8191879251754</v>
+        <v>719.6953328622245</v>
       </c>
       <c r="D26" t="n">
-        <v>687.575107355611</v>
+        <v>706.7139709983563</v>
       </c>
       <c r="E26" t="n">
-        <v>702.6852290659051</v>
+        <v>708.6636250955381</v>
       </c>
       <c r="F26" t="n">
-        <v>2892200</v>
+        <v>1042900</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45870</v>
+        <v>45880</v>
       </c>
       <c r="B27" t="n">
-        <v>686.1925048828125</v>
+        <v>717.5169067382812</v>
       </c>
       <c r="C27" t="n">
-        <v>689.7835066871638</v>
+        <v>728.0114162181982</v>
       </c>
       <c r="D27" t="n">
-        <v>679.8858178299772</v>
+        <v>715.7363415143743</v>
       </c>
       <c r="E27" t="n">
-        <v>686.3715510452078</v>
+        <v>720.1927634953054</v>
       </c>
       <c r="F27" t="n">
-        <v>1627100</v>
+        <v>1179700</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45873</v>
+        <v>45881</v>
       </c>
       <c r="B28" t="n">
-        <v>695.6822509765625</v>
+        <v>737.88916015625</v>
       </c>
       <c r="C28" t="n">
-        <v>695.7718044065165</v>
+        <v>739.4409542252636</v>
       </c>
       <c r="D28" t="n">
-        <v>689.2562611281992</v>
+        <v>719.6754485651294</v>
       </c>
       <c r="E28" t="n">
-        <v>691.9221604880988</v>
+        <v>721.7147168929212</v>
       </c>
       <c r="F28" t="n">
-        <v>1025600</v>
+        <v>1461800</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45874</v>
+        <v>45882</v>
       </c>
       <c r="B29" t="n">
-        <v>686.0034790039062</v>
+        <v>751.5966796875</v>
       </c>
       <c r="C29" t="n">
-        <v>691.9719270773378</v>
+        <v>752.2233715539303</v>
       </c>
       <c r="D29" t="n">
-        <v>680.6418085798671</v>
+        <v>743.6088780293874</v>
       </c>
       <c r="E29" t="n">
-        <v>691.0666784529191</v>
+        <v>746.6826553130308</v>
       </c>
       <c r="F29" t="n">
-        <v>1261200</v>
+        <v>2011900</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45875</v>
+        <v>45883</v>
       </c>
       <c r="B30" t="n">
-        <v>687.3264770507812</v>
+        <v>751.2385864257812</v>
       </c>
       <c r="C30" t="n">
-        <v>688.7887176328952</v>
+        <v>753.0191514657981</v>
       </c>
       <c r="D30" t="n">
-        <v>681.8354855939474</v>
+        <v>740.644567472852</v>
       </c>
       <c r="E30" t="n">
-        <v>684.0338857449923</v>
+        <v>743.3502953348344</v>
       </c>
       <c r="F30" t="n">
-        <v>1218700</v>
+        <v>1577400</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45876</v>
+        <v>45884</v>
       </c>
       <c r="B31" t="n">
-        <v>709.3699340820312</v>
+        <v>738.2572021484375</v>
       </c>
       <c r="C31" t="n">
-        <v>713.1300854611995</v>
+        <v>743.2210124078517</v>
       </c>
       <c r="D31" t="n">
-        <v>702.9041154216311</v>
+        <v>732.7861248083158</v>
       </c>
       <c r="E31" t="n">
-        <v>710.2652255668406</v>
+        <v>734.6164755781649</v>
       </c>
       <c r="F31" t="n">
-        <v>1723800</v>
+        <v>1635100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45877</v>
+        <v>45887</v>
       </c>
       <c r="B32" t="n">
-        <v>718.5215454101562</v>
+        <v>743.6188354492188</v>
       </c>
       <c r="C32" t="n">
-        <v>719.6953328622245</v>
+        <v>744.0664811703009</v>
       </c>
       <c r="D32" t="n">
-        <v>706.7139709983563</v>
+        <v>735.5514981993795</v>
       </c>
       <c r="E32" t="n">
-        <v>708.6636250955381</v>
+        <v>735.7802692663857</v>
       </c>
       <c r="F32" t="n">
-        <v>1042900</v>
+        <v>1086400</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45880</v>
+        <v>45888</v>
       </c>
       <c r="B33" t="n">
-        <v>717.516845703125</v>
+        <v>739.6995239257812</v>
       </c>
       <c r="C33" t="n">
-        <v>728.0113542903326</v>
+        <v>751.7160151865168</v>
       </c>
       <c r="D33" t="n">
-        <v>715.7362806306809</v>
+        <v>737.8095519854651</v>
       </c>
       <c r="E33" t="n">
-        <v>720.192702232529</v>
+        <v>747.5878147268214</v>
       </c>
       <c r="F33" t="n">
-        <v>1179700</v>
+        <v>1121300</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45881</v>
+        <v>45889</v>
       </c>
       <c r="B34" t="n">
-        <v>737.88916015625</v>
+        <v>745.5486450195312</v>
       </c>
       <c r="C34" t="n">
-        <v>739.4409542252636</v>
+        <v>749.4778852857579</v>
       </c>
       <c r="D34" t="n">
-        <v>719.6754485651294</v>
+        <v>734.2981233783457</v>
       </c>
       <c r="E34" t="n">
-        <v>721.7147168929212</v>
+        <v>746.8517536901128</v>
       </c>
       <c r="F34" t="n">
-        <v>1461800</v>
+        <v>1368400</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45882</v>
+        <v>45890</v>
       </c>
       <c r="B35" t="n">
-        <v>751.5967407226562</v>
+        <v>731.5327758789062</v>
       </c>
       <c r="C35" t="n">
-        <v>752.2234326399786</v>
+        <v>737.6006735196901</v>
       </c>
       <c r="D35" t="n">
-        <v>743.6089384158755</v>
+        <v>728.2600381467336</v>
       </c>
       <c r="E35" t="n">
-        <v>746.6827159491323</v>
+        <v>735.4719125675261</v>
       </c>
       <c r="F35" t="n">
-        <v>2011900</v>
+        <v>952700</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45883</v>
+        <v>45891</v>
       </c>
       <c r="B36" t="n">
-        <v>751.2386474609375</v>
+        <v>750.9203491210938</v>
       </c>
       <c r="C36" t="n">
-        <v>753.0192126456183</v>
+        <v>757.5652143794587</v>
       </c>
       <c r="D36" t="n">
-        <v>740.6446276472863</v>
+        <v>736.476684581791</v>
       </c>
       <c r="E36" t="n">
-        <v>743.3503557290982</v>
+        <v>737.7797933856677</v>
       </c>
       <c r="F36" t="n">
-        <v>1577400</v>
+        <v>1456000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45884</v>
+        <v>45894</v>
       </c>
       <c r="B37" t="n">
-        <v>738.2572021484375</v>
+        <v>750.4925537109375</v>
       </c>
       <c r="C37" t="n">
-        <v>743.2210124078517</v>
+        <v>754.2725585617695</v>
       </c>
       <c r="D37" t="n">
-        <v>732.7861248083158</v>
+        <v>748.1350216535994</v>
       </c>
       <c r="E37" t="n">
-        <v>734.6164755781649</v>
+        <v>750.7810068349245</v>
       </c>
       <c r="F37" t="n">
-        <v>1635100</v>
+        <v>731100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45887</v>
+        <v>45895</v>
       </c>
       <c r="B38" t="n">
-        <v>743.6188354492188</v>
+        <v>759.1866455078125</v>
       </c>
       <c r="C38" t="n">
-        <v>744.0664811703009</v>
+        <v>759.4850557837487</v>
       </c>
       <c r="D38" t="n">
-        <v>735.5514981993795</v>
+        <v>751.9349418744811</v>
       </c>
       <c r="E38" t="n">
-        <v>735.7802692663857</v>
+        <v>754.7799484095973</v>
       </c>
       <c r="F38" t="n">
-        <v>1086400</v>
+        <v>860100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45888</v>
+        <v>45896</v>
       </c>
       <c r="B39" t="n">
-        <v>739.6995239257812</v>
+        <v>765.9508666992188</v>
       </c>
       <c r="C39" t="n">
-        <v>751.7160151865168</v>
+        <v>766.5278337026814</v>
       </c>
       <c r="D39" t="n">
-        <v>737.8095519854651</v>
+        <v>753.8050525273063</v>
       </c>
       <c r="E39" t="n">
-        <v>747.5878147268214</v>
+        <v>756.0034528459821</v>
       </c>
       <c r="F39" t="n">
-        <v>1121300</v>
+        <v>1140700</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45889</v>
+        <v>45897</v>
       </c>
       <c r="B40" t="n">
-        <v>745.5486450195312</v>
+        <v>759.4451904296875</v>
       </c>
       <c r="C40" t="n">
-        <v>749.4778852857579</v>
+        <v>769.104089286226</v>
       </c>
       <c r="D40" t="n">
-        <v>734.2981233783457</v>
+        <v>756.8687838309672</v>
       </c>
       <c r="E40" t="n">
-        <v>746.8517536901128</v>
+        <v>765.9507764662017</v>
       </c>
       <c r="F40" t="n">
-        <v>1368400</v>
+        <v>985400</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45890</v>
+        <v>45898</v>
       </c>
       <c r="B41" t="n">
-        <v>731.5327758789062</v>
+        <v>738.7147827148438</v>
       </c>
       <c r="C41" t="n">
-        <v>737.6006735196901</v>
+        <v>749.6370228100703</v>
       </c>
       <c r="D41" t="n">
-        <v>728.2600381467336</v>
+        <v>735.8996478230431</v>
       </c>
       <c r="E41" t="n">
-        <v>735.4719125675261</v>
+        <v>749.0402023130272</v>
       </c>
       <c r="F41" t="n">
-        <v>952700</v>
+        <v>1317800</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45891</v>
+        <v>45902</v>
       </c>
       <c r="B42" t="n">
-        <v>750.9202270507812</v>
+        <v>722.032958984375</v>
       </c>
       <c r="C42" t="n">
-        <v>757.5650912289507</v>
+        <v>723.3758961877257</v>
       </c>
       <c r="D42" t="n">
-        <v>736.4765648594541</v>
+        <v>712.4337417261006</v>
       </c>
       <c r="E42" t="n">
-        <v>737.7796734514963</v>
+        <v>713.4384401682114</v>
       </c>
       <c r="F42" t="n">
-        <v>1456000</v>
+        <v>1867400</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45894</v>
+        <v>45903</v>
       </c>
       <c r="B43" t="n">
-        <v>750.4926147460938</v>
+        <v>732.9453125</v>
       </c>
       <c r="C43" t="n">
-        <v>754.2726199043415</v>
+        <v>734.4175102367324</v>
       </c>
       <c r="D43" t="n">
-        <v>748.1350824970252</v>
+        <v>725.7234807452637</v>
       </c>
       <c r="E43" t="n">
-        <v>750.7810678935397</v>
+        <v>728.3694659632006</v>
       </c>
       <c r="F43" t="n">
-        <v>731100</v>
+        <v>1330300</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45895</v>
+        <v>45904</v>
       </c>
       <c r="B44" t="n">
-        <v>759.1865844726562</v>
+        <v>749.4679565429688</v>
       </c>
       <c r="C44" t="n">
-        <v>759.4849947246016</v>
+        <v>752.9197405458762</v>
       </c>
       <c r="D44" t="n">
-        <v>751.9348814223289</v>
+        <v>731.562612517756</v>
       </c>
       <c r="E44" t="n">
-        <v>754.7798877287195</v>
+        <v>733.1740886228896</v>
       </c>
       <c r="F44" t="n">
-        <v>860100</v>
+        <v>1532700</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45896</v>
+        <v>45905</v>
       </c>
       <c r="B45" t="n">
-        <v>765.9508056640625</v>
+        <v>777.5892944335938</v>
       </c>
       <c r="C45" t="n">
-        <v>766.5277726215492</v>
+        <v>778.9818958395513</v>
       </c>
       <c r="D45" t="n">
-        <v>753.804992459995</v>
+        <v>762.2105719186685</v>
       </c>
       <c r="E45" t="n">
-        <v>756.0033926034903</v>
+        <v>770.8051514113896</v>
       </c>
       <c r="F45" t="n">
-        <v>1140700</v>
+        <v>1887300</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45897</v>
+        <v>45908</v>
       </c>
       <c r="B46" t="n">
-        <v>759.4451904296875</v>
+        <v>792.062744140625</v>
       </c>
       <c r="C46" t="n">
-        <v>769.104089286226</v>
+        <v>794.4998724192802</v>
       </c>
       <c r="D46" t="n">
-        <v>756.8687838309672</v>
+        <v>782.6127019813334</v>
       </c>
       <c r="E46" t="n">
-        <v>765.9507764662017</v>
+        <v>785.497475978793</v>
       </c>
       <c r="F46" t="n">
-        <v>985400</v>
+        <v>1284500</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45898</v>
+        <v>45909</v>
       </c>
       <c r="B47" t="n">
-        <v>738.71484375</v>
+        <v>800.8961181640625</v>
       </c>
       <c r="C47" t="n">
-        <v>749.6370847476596</v>
+        <v>801.6024063886509</v>
       </c>
       <c r="D47" t="n">
-        <v>735.8997086256032</v>
+        <v>788.9492646844166</v>
       </c>
       <c r="E47" t="n">
-        <v>749.040264201305</v>
+        <v>791.018343718694</v>
       </c>
       <c r="F47" t="n">
-        <v>1317800</v>
+        <v>1324100</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45902</v>
+        <v>45910</v>
       </c>
       <c r="B48" t="n">
-        <v>722.032958984375</v>
+        <v>788.9691162109375</v>
       </c>
       <c r="C48" t="n">
-        <v>723.3758961877257</v>
+        <v>805.3425188811863</v>
       </c>
       <c r="D48" t="n">
-        <v>712.4337417261006</v>
+        <v>786.8602695469341</v>
       </c>
       <c r="E48" t="n">
-        <v>713.4384401682114</v>
+        <v>802.5771696842795</v>
       </c>
       <c r="F48" t="n">
-        <v>1867400</v>
+        <v>1634300</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45903</v>
+        <v>45911</v>
       </c>
       <c r="B49" t="n">
-        <v>732.9453735351562</v>
+        <v>799.9312133789062</v>
       </c>
       <c r="C49" t="n">
-        <v>734.4175713944842</v>
+        <v>804.8950239391984</v>
       </c>
       <c r="D49" t="n">
-        <v>725.7235411790305</v>
+        <v>794.3109609264474</v>
       </c>
       <c r="E49" t="n">
-        <v>728.3695266173087</v>
+        <v>795.4847484866823</v>
       </c>
       <c r="F49" t="n">
-        <v>1330300</v>
+        <v>1297800</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45904</v>
+        <v>45912</v>
       </c>
       <c r="B50" t="n">
-        <v>749.4679565429688</v>
+        <v>809.590087890625</v>
       </c>
       <c r="C50" t="n">
-        <v>752.9197405458762</v>
+        <v>811.4900777522547</v>
       </c>
       <c r="D50" t="n">
-        <v>731.562612517756</v>
+        <v>802.0598890484076</v>
       </c>
       <c r="E50" t="n">
-        <v>733.1740886228896</v>
+        <v>804.26824628101</v>
       </c>
       <c r="F50" t="n">
-        <v>1532700</v>
+        <v>1019700</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45905</v>
+        <v>45915</v>
       </c>
       <c r="B51" t="n">
-        <v>777.5892944335938</v>
+        <v>862.7391357421875</v>
       </c>
       <c r="C51" t="n">
-        <v>778.9818958395513</v>
+        <v>864.1516514183313</v>
       </c>
       <c r="D51" t="n">
-        <v>762.2105719186685</v>
+        <v>829.534665583078</v>
       </c>
       <c r="E51" t="n">
-        <v>770.8051514113896</v>
+        <v>830.5393640317703</v>
       </c>
       <c r="F51" t="n">
-        <v>1887300</v>
+        <v>2702300</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45908</v>
+        <v>45916</v>
       </c>
       <c r="B52" t="n">
-        <v>792.062744140625</v>
+        <v>873.8006591796875</v>
       </c>
       <c r="C52" t="n">
-        <v>794.4998724192802</v>
+        <v>876.8247116698689</v>
       </c>
       <c r="D52" t="n">
-        <v>782.6127019813334</v>
+        <v>863.0077400709183</v>
       </c>
       <c r="E52" t="n">
-        <v>785.497475978793</v>
+        <v>875.3126854247781</v>
       </c>
       <c r="F52" t="n">
-        <v>1284500</v>
+        <v>1832400</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45909</v>
+        <v>45917</v>
       </c>
       <c r="B53" t="n">
-        <v>800.8960571289062</v>
+        <v>867.6830444335938</v>
       </c>
       <c r="C53" t="n">
-        <v>801.6023452996695</v>
+        <v>873.0148434222401</v>
       </c>
       <c r="D53" t="n">
-        <v>788.9492045597131</v>
+        <v>856.6513363049863</v>
       </c>
       <c r="E53" t="n">
-        <v>791.018283436309</v>
+        <v>863.6642505797543</v>
       </c>
       <c r="F53" t="n">
-        <v>1324100</v>
+        <v>1553300</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45910</v>
+        <v>45918</v>
       </c>
       <c r="B54" t="n">
-        <v>788.9691772460938</v>
+        <v>922.9209594726562</v>
       </c>
       <c r="C54" t="n">
-        <v>805.3425811829995</v>
+        <v>933.7437495972807</v>
       </c>
       <c r="D54" t="n">
-        <v>786.8603304189487</v>
+        <v>911.2128957400749</v>
       </c>
       <c r="E54" t="n">
-        <v>802.5772317721636</v>
+        <v>923.7863795404029</v>
       </c>
       <c r="F54" t="n">
-        <v>1634300</v>
+        <v>3176100</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45911</v>
+        <v>45919</v>
       </c>
       <c r="B55" t="n">
-        <v>799.93115234375</v>
+        <v>927.2481079101562</v>
       </c>
       <c r="C55" t="n">
-        <v>804.8949625253009</v>
+        <v>933.7139262264777</v>
       </c>
       <c r="D55" t="n">
-        <v>794.3109003201192</v>
+        <v>921.0011035324992</v>
       </c>
       <c r="E55" t="n">
-        <v>795.4846877907936</v>
+        <v>921.2000639312239</v>
       </c>
       <c r="F55" t="n">
-        <v>1297800</v>
+        <v>2410200</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45912</v>
+        <v>45922</v>
       </c>
       <c r="B56" t="n">
-        <v>809.590087890625</v>
+        <v>952.7632446289062</v>
       </c>
       <c r="C56" t="n">
-        <v>811.4900777522547</v>
+        <v>959.4677915555224</v>
       </c>
       <c r="D56" t="n">
-        <v>802.0598890484076</v>
+        <v>948.575422438789</v>
       </c>
       <c r="E56" t="n">
-        <v>804.26824628101</v>
+        <v>955.8668327568698</v>
       </c>
       <c r="F56" t="n">
-        <v>1019700</v>
+        <v>1885000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45915</v>
+        <v>45923</v>
       </c>
       <c r="B57" t="n">
-        <v>862.7391357421875</v>
+        <v>958.4431762695312</v>
       </c>
       <c r="C57" t="n">
-        <v>864.1516514183313</v>
+        <v>972.33968274833</v>
       </c>
       <c r="D57" t="n">
-        <v>829.534665583078</v>
+        <v>950.9726595747106</v>
       </c>
       <c r="E57" t="n">
-        <v>830.5393640317703</v>
+        <v>959.3384069891529</v>
       </c>
       <c r="F57" t="n">
-        <v>2702300</v>
+        <v>1664800</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45916</v>
+        <v>45924</v>
       </c>
       <c r="B58" t="n">
-        <v>873.8005981445312</v>
+        <v>941.9603271484375</v>
       </c>
       <c r="C58" t="n">
-        <v>876.8246504234819</v>
+        <v>948.5852774788157</v>
       </c>
       <c r="D58" t="n">
-        <v>863.0076797896497</v>
+        <v>936.0018364877402</v>
       </c>
       <c r="E58" t="n">
-        <v>875.3126242840066</v>
+        <v>944.7256763854742</v>
       </c>
       <c r="F58" t="n">
-        <v>1832400</v>
+        <v>1400700</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45917</v>
+        <v>45925</v>
       </c>
       <c r="B59" t="n">
-        <v>867.6830444335938</v>
+        <v>944.556640625</v>
       </c>
       <c r="C59" t="n">
-        <v>873.0148434222401</v>
+        <v>947.650271664786</v>
       </c>
       <c r="D59" t="n">
-        <v>856.6513363049863</v>
+        <v>932.1920128794735</v>
       </c>
       <c r="E59" t="n">
-        <v>863.6642505797543</v>
+        <v>933.2663505418556</v>
       </c>
       <c r="F59" t="n">
-        <v>1553300</v>
+        <v>1272600</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45918</v>
+        <v>45926</v>
       </c>
       <c r="B60" t="n">
-        <v>922.9209594726562</v>
+        <v>946.5162353515625</v>
       </c>
       <c r="C60" t="n">
-        <v>933.7437495972807</v>
+        <v>950.1967294896816</v>
       </c>
       <c r="D60" t="n">
-        <v>911.2128957400749</v>
+        <v>937.7923349603046</v>
       </c>
       <c r="E60" t="n">
-        <v>923.7863795404029</v>
+        <v>941.2639722882104</v>
       </c>
       <c r="F60" t="n">
-        <v>3176100</v>
+        <v>955200</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45919</v>
+        <v>45929</v>
       </c>
       <c r="B61" t="n">
-        <v>927.2481689453125</v>
+        <v>957.5479125976562</v>
       </c>
       <c r="C61" t="n">
-        <v>933.71398768724</v>
+        <v>966.9581871957705</v>
       </c>
       <c r="D61" t="n">
-        <v>921.0011641564529</v>
+        <v>957.3091843988358</v>
       </c>
       <c r="E61" t="n">
-        <v>921.200124568274</v>
+        <v>958.6620180016125</v>
       </c>
       <c r="F61" t="n">
-        <v>2410200</v>
+        <v>1213800</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45922</v>
+        <v>45930</v>
       </c>
       <c r="B62" t="n">
-        <v>952.7632446289062</v>
+        <v>962.9991455078125</v>
       </c>
       <c r="C62" t="n">
-        <v>959.4677915555224</v>
+        <v>970.5094302866358</v>
       </c>
       <c r="D62" t="n">
-        <v>948.575422438789</v>
+        <v>958.0055246823517</v>
       </c>
       <c r="E62" t="n">
-        <v>955.8668327568698</v>
+        <v>962.9493598707529</v>
       </c>
       <c r="F62" t="n">
-        <v>1885000</v>
+        <v>1303600</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45923</v>
+        <v>45931</v>
       </c>
       <c r="B63" t="n">
-        <v>958.4432373046875</v>
+        <v>997.994140625</v>
       </c>
       <c r="C63" t="n">
-        <v>972.3397446684373</v>
+        <v>1000.07311597777</v>
       </c>
       <c r="D63" t="n">
-        <v>950.9727201341327</v>
+        <v>959.7463248400675</v>
       </c>
       <c r="E63" t="n">
-        <v>959.3384680813189</v>
+        <v>960.5321486234592</v>
       </c>
       <c r="F63" t="n">
-        <v>1664800</v>
+        <v>1963800</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45924</v>
+        <v>45932</v>
       </c>
       <c r="B64" t="n">
-        <v>941.9603881835938</v>
+        <v>1024.752685546875</v>
       </c>
       <c r="C64" t="n">
-        <v>948.5853389432414</v>
+        <v>1034.759719850982</v>
       </c>
       <c r="D64" t="n">
-        <v>936.0018971368107</v>
+        <v>1016.51619846569</v>
       </c>
       <c r="E64" t="n">
-        <v>944.7257375998137</v>
+        <v>1033.536207484329</v>
       </c>
       <c r="F64" t="n">
-        <v>1400700</v>
+        <v>1689100</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45925</v>
+        <v>45933</v>
       </c>
       <c r="B65" t="n">
-        <v>944.5565795898438</v>
+        <v>1026.791870117188</v>
       </c>
       <c r="C65" t="n">
-        <v>947.6502104297263</v>
+        <v>1034.381751348888</v>
       </c>
       <c r="D65" t="n">
-        <v>932.1919526432921</v>
+        <v>1020.067408988492</v>
       </c>
       <c r="E65" t="n">
-        <v>933.2662902362529</v>
+        <v>1025.578314833136</v>
       </c>
       <c r="F65" t="n">
-        <v>1272600</v>
+        <v>1352300</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45926</v>
+        <v>45936</v>
       </c>
       <c r="B66" t="n">
-        <v>946.5162963867188</v>
+        <v>1037.813598632812</v>
       </c>
       <c r="C66" t="n">
-        <v>950.1967907621708</v>
+        <v>1053.4309877457</v>
       </c>
       <c r="D66" t="n">
-        <v>937.7923954329088</v>
+        <v>1034.630353763713</v>
       </c>
       <c r="E66" t="n">
-        <v>941.2640329846797</v>
+        <v>1034.968531790051</v>
       </c>
       <c r="F66" t="n">
-        <v>955200</v>
+        <v>1385400</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45929</v>
+        <v>45937</v>
       </c>
       <c r="B67" t="n">
-        <v>957.5479125976562</v>
+        <v>997.0291748046875</v>
       </c>
       <c r="C67" t="n">
-        <v>966.9581871957705</v>
+        <v>1039.355404210904</v>
       </c>
       <c r="D67" t="n">
-        <v>957.3091843988358</v>
+        <v>995.7360232809268</v>
       </c>
       <c r="E67" t="n">
-        <v>958.6620180016125</v>
+        <v>1037.346007392725</v>
       </c>
       <c r="F67" t="n">
-        <v>1213800</v>
+        <v>1667800</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45930</v>
+        <v>45938</v>
       </c>
       <c r="B68" t="n">
-        <v>962.9990844726562</v>
+        <v>982.6154174804688</v>
       </c>
       <c r="C68" t="n">
-        <v>970.5093687754757</v>
+        <v>986.3755687998695</v>
       </c>
       <c r="D68" t="n">
-        <v>958.0054639636927</v>
+        <v>972.2800406300264</v>
       </c>
       <c r="E68" t="n">
-        <v>962.9492988387522</v>
+        <v>972.8072826706141</v>
       </c>
       <c r="F68" t="n">
-        <v>1303600</v>
+        <v>1947000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45931</v>
+        <v>45939</v>
       </c>
       <c r="B69" t="n">
-        <v>997.994140625</v>
+        <v>975.3836669921875</v>
       </c>
       <c r="C69" t="n">
-        <v>1000.07311597777</v>
+        <v>982.3369600679632</v>
       </c>
       <c r="D69" t="n">
-        <v>959.7463248400675</v>
+        <v>966.4011841222308</v>
       </c>
       <c r="E69" t="n">
-        <v>960.5321486234592</v>
+        <v>980.1683704841994</v>
       </c>
       <c r="F69" t="n">
-        <v>1963800</v>
+        <v>1496000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45932</v>
+        <v>45940</v>
       </c>
       <c r="B70" t="n">
-        <v>1024.752685546875</v>
+        <v>931.2669067382812</v>
       </c>
       <c r="C70" t="n">
-        <v>1034.759719850982</v>
+        <v>971.066517859779</v>
       </c>
       <c r="D70" t="n">
-        <v>1016.51619846569</v>
+        <v>930.4909793425905</v>
       </c>
       <c r="E70" t="n">
-        <v>1033.536207484329</v>
+        <v>965.5854833078719</v>
       </c>
       <c r="F70" t="n">
-        <v>1689100</v>
+        <v>2933900</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45933</v>
+        <v>45943</v>
       </c>
       <c r="B71" t="n">
-        <v>1026.7919921875</v>
+        <v>979.48193359375</v>
       </c>
       <c r="C71" t="n">
-        <v>1034.381874321525</v>
+        <v>979.9992184939867</v>
       </c>
       <c r="D71" t="n">
-        <v>1020.067530259366</v>
+        <v>961.884957714602</v>
       </c>
       <c r="E71" t="n">
-        <v>1025.578436759175</v>
+        <v>966.619935977474</v>
       </c>
       <c r="F71" t="n">
-        <v>1352300</v>
+        <v>2223900</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45936</v>
+        <v>45944</v>
       </c>
       <c r="B72" t="n">
-        <v>1037.813598632812</v>
+        <v>978.009765625</v>
       </c>
       <c r="C72" t="n">
-        <v>1053.4309877457</v>
+        <v>988.2555890982037</v>
       </c>
       <c r="D72" t="n">
-        <v>1034.630353763713</v>
+        <v>960.9201169996737</v>
       </c>
       <c r="E72" t="n">
-        <v>1034.968531790051</v>
+        <v>962.3724611868238</v>
       </c>
       <c r="F72" t="n">
-        <v>1385400</v>
+        <v>2422100</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45937</v>
+        <v>45945</v>
       </c>
       <c r="B73" t="n">
-        <v>997.0291748046875</v>
+        <v>1004.499694824219</v>
       </c>
       <c r="C73" t="n">
-        <v>1039.355404210904</v>
+        <v>1027.567747657607</v>
       </c>
       <c r="D73" t="n">
-        <v>995.7360232809268</v>
+        <v>988.3152346847494</v>
       </c>
       <c r="E73" t="n">
-        <v>1037.346007392725</v>
+        <v>1024.71284502609</v>
       </c>
       <c r="F73" t="n">
-        <v>1667800</v>
+        <v>2900300</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>45938</v>
+        <v>45946</v>
       </c>
       <c r="B74" t="n">
-        <v>982.6154174804688</v>
+        <v>1014.228332519531</v>
       </c>
       <c r="C74" t="n">
-        <v>986.3755687998695</v>
+        <v>1043.861654682999</v>
       </c>
       <c r="D74" t="n">
-        <v>972.2800406300264</v>
+        <v>1005.782927684944</v>
       </c>
       <c r="E74" t="n">
-        <v>972.8072826706141</v>
+        <v>1031.715901982806</v>
       </c>
       <c r="F74" t="n">
-        <v>1947000</v>
+        <v>1938400</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45939</v>
+        <v>45947</v>
       </c>
       <c r="B75" t="n">
-        <v>975.3836059570312</v>
+        <v>1023.857421875</v>
       </c>
       <c r="C75" t="n">
-        <v>982.336898597701</v>
+        <v>1027.339016508636</v>
       </c>
       <c r="D75" t="n">
-        <v>966.4011236491583</v>
+        <v>1009.662443754462</v>
       </c>
       <c r="E75" t="n">
-        <v>980.1683091496377</v>
+        <v>1015.223074469286</v>
       </c>
       <c r="F75" t="n">
-        <v>1496000</v>
+        <v>1663700</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45940</v>
+        <v>45950</v>
       </c>
       <c r="B76" t="n">
-        <v>931.2669067382812</v>
+        <v>1036.669677734375</v>
       </c>
       <c r="C76" t="n">
-        <v>971.066517859779</v>
+        <v>1046.637005062504</v>
       </c>
       <c r="D76" t="n">
-        <v>930.4909793425905</v>
+        <v>1026.065701398139</v>
       </c>
       <c r="E76" t="n">
-        <v>965.5854833078719</v>
+        <v>1026.32434385232</v>
       </c>
       <c r="F76" t="n">
-        <v>2933900</v>
+        <v>1271700</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45943</v>
+        <v>45951</v>
       </c>
       <c r="B77" t="n">
-        <v>979.48193359375</v>
+        <v>1019.629821777344</v>
       </c>
       <c r="C77" t="n">
-        <v>979.9992184939867</v>
+        <v>1032.024260430225</v>
       </c>
       <c r="D77" t="n">
-        <v>961.884957714602</v>
+        <v>1018.764401639803</v>
       </c>
       <c r="E77" t="n">
-        <v>966.619935977474</v>
+        <v>1030.860490737761</v>
       </c>
       <c r="F77" t="n">
-        <v>2223900</v>
+        <v>1072200</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45944</v>
+        <v>45952</v>
       </c>
       <c r="B78" t="n">
-        <v>978.009765625</v>
+        <v>1006.250427246094</v>
       </c>
       <c r="C78" t="n">
-        <v>988.2555890982037</v>
+        <v>1027.746832094003</v>
       </c>
       <c r="D78" t="n">
-        <v>960.9201169996737</v>
+        <v>992.4234993971954</v>
       </c>
       <c r="E78" t="n">
-        <v>962.3724611868238</v>
+        <v>1021.052121390534</v>
       </c>
       <c r="F78" t="n">
-        <v>2422100</v>
+        <v>1328600</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45945</v>
+        <v>45953</v>
       </c>
       <c r="B79" t="n">
-        <v>1004.499755859375</v>
+        <v>1030.959838867188</v>
       </c>
       <c r="C79" t="n">
-        <v>1027.567810094419</v>
+        <v>1035.028296682167</v>
       </c>
       <c r="D79" t="n">
-        <v>988.3152947365096</v>
+        <v>999.2176107806217</v>
       </c>
       <c r="E79" t="n">
-        <v>1024.712907289433</v>
+        <v>999.2375250346631</v>
       </c>
       <c r="F79" t="n">
-        <v>2900300</v>
+        <v>1318200</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45946</v>
+        <v>45954</v>
       </c>
       <c r="B80" t="n">
-        <v>1014.228271484375</v>
+        <v>1027.667236328125</v>
       </c>
       <c r="C80" t="n">
-        <v>1043.861591864541</v>
+        <v>1037.913120524609</v>
       </c>
       <c r="D80" t="n">
-        <v>1005.782867158023</v>
+        <v>1026.752152025289</v>
       </c>
       <c r="E80" t="n">
-        <v>1031.715839895267</v>
+        <v>1032.471914631551</v>
       </c>
       <c r="F80" t="n">
-        <v>1938400</v>
+        <v>1032700</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45947</v>
+        <v>45957</v>
       </c>
       <c r="B81" t="n">
-        <v>1023.857299804688</v>
+        <v>1054.406005859375</v>
       </c>
       <c r="C81" t="n">
-        <v>1027.338894023227</v>
+        <v>1055.152061934929</v>
       </c>
       <c r="D81" t="n">
-        <v>1009.662323376559</v>
+        <v>1043.841856686664</v>
       </c>
       <c r="E81" t="n">
-        <v>1015.222953428411</v>
+        <v>1044.48846290449</v>
       </c>
       <c r="F81" t="n">
-        <v>1663700</v>
+        <v>1265600</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45950</v>
+        <v>45958</v>
       </c>
       <c r="B82" t="n">
-        <v>1036.669677734375</v>
+        <v>1046.9453125</v>
       </c>
       <c r="C82" t="n">
-        <v>1046.637005062504</v>
+        <v>1055.062435573884</v>
       </c>
       <c r="D82" t="n">
-        <v>1026.065701398139</v>
+        <v>1046.19925651894</v>
       </c>
       <c r="E82" t="n">
-        <v>1026.32434385232</v>
+        <v>1051.242662950802</v>
       </c>
       <c r="F82" t="n">
-        <v>1271700</v>
+        <v>856900</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45951</v>
+        <v>45959</v>
       </c>
       <c r="B83" t="n">
-        <v>1019.629760742188</v>
+        <v>1067.0986328125</v>
       </c>
       <c r="C83" t="n">
-        <v>1032.024198653137</v>
+        <v>1073.994499299318</v>
       </c>
       <c r="D83" t="n">
-        <v>1018.764340656451</v>
+        <v>1061.119595793677</v>
       </c>
       <c r="E83" t="n">
-        <v>1030.860429030336</v>
+        <v>1066.919329822474</v>
       </c>
       <c r="F83" t="n">
-        <v>1072200</v>
+        <v>1530000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45952</v>
+        <v>45960</v>
       </c>
       <c r="B84" t="n">
-        <v>1006.25048828125</v>
+        <v>1071.692504882812</v>
       </c>
       <c r="C84" t="n">
-        <v>1027.746894433046</v>
+        <v>1082.315294646034</v>
       </c>
       <c r="D84" t="n">
-        <v>992.4235595936651</v>
+        <v>1066.869449111723</v>
       </c>
       <c r="E84" t="n">
-        <v>1021.052183323502</v>
+        <v>1068.932284990714</v>
       </c>
       <c r="F84" t="n">
-        <v>1328600</v>
+        <v>1283100</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45953</v>
+        <v>45961</v>
       </c>
       <c r="B85" t="n">
-        <v>1030.959838867188</v>
+        <v>1055.529174804688</v>
       </c>
       <c r="C85" t="n">
-        <v>1035.028296682167</v>
+        <v>1069.530134670791</v>
       </c>
       <c r="D85" t="n">
-        <v>999.2176107806217</v>
+        <v>1047.72657555282</v>
       </c>
       <c r="E85" t="n">
-        <v>999.2375250346631</v>
+        <v>1067.935749182207</v>
       </c>
       <c r="F85" t="n">
-        <v>1318200</v>
+        <v>1179400</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45954</v>
+        <v>45964</v>
       </c>
       <c r="B86" t="n">
-        <v>1027.667236328125</v>
+        <v>1063.092651367188</v>
       </c>
       <c r="C86" t="n">
-        <v>1037.913120524609</v>
+        <v>1069.649739772258</v>
       </c>
       <c r="D86" t="n">
-        <v>1026.752152025289</v>
+        <v>1059.276076554389</v>
       </c>
       <c r="E86" t="n">
-        <v>1032.471914631551</v>
+        <v>1059.306000933798</v>
       </c>
       <c r="F86" t="n">
-        <v>1032700</v>
+        <v>868100</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45957</v>
+        <v>45965</v>
       </c>
       <c r="B87" t="n">
-        <v>1054.405883789062</v>
+        <v>1026.540893554688</v>
       </c>
       <c r="C87" t="n">
-        <v>1055.151939778245</v>
+        <v>1059.545173457092</v>
       </c>
       <c r="D87" t="n">
-        <v>1043.84173583938</v>
+        <v>1025.23541206643</v>
       </c>
       <c r="E87" t="n">
-        <v>1044.488341982348</v>
+        <v>1046.281617777473</v>
       </c>
       <c r="F87" t="n">
-        <v>1265600</v>
+        <v>1735100</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45958</v>
+        <v>45966</v>
       </c>
       <c r="B88" t="n">
-        <v>1046.9453125</v>
+        <v>1040.103271484375</v>
       </c>
       <c r="C88" t="n">
-        <v>1055.062435573884</v>
+        <v>1046.96921330609</v>
       </c>
       <c r="D88" t="n">
-        <v>1046.19925651894</v>
+        <v>1027.198565779532</v>
       </c>
       <c r="E88" t="n">
-        <v>1051.242662950802</v>
+        <v>1027.497444631754</v>
       </c>
       <c r="F88" t="n">
-        <v>856900</v>
+        <v>1169400</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45959</v>
+        <v>45967</v>
       </c>
       <c r="B89" t="n">
-        <v>1067.0986328125</v>
+        <v>1025.604125976562</v>
       </c>
       <c r="C89" t="n">
-        <v>1073.994499299318</v>
+        <v>1037.891125197865</v>
       </c>
       <c r="D89" t="n">
-        <v>1061.119595793677</v>
+        <v>1022.853759150235</v>
       </c>
       <c r="E89" t="n">
-        <v>1066.919329822474</v>
+        <v>1036.24686564937</v>
       </c>
       <c r="F89" t="n">
-        <v>1530000</v>
+        <v>1073000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45960</v>
+        <v>45968</v>
       </c>
       <c r="B90" t="n">
-        <v>1071.692504882812</v>
+        <v>1013.406921386719</v>
       </c>
       <c r="C90" t="n">
-        <v>1082.315294646034</v>
+        <v>1031.782497319645</v>
       </c>
       <c r="D90" t="n">
-        <v>1066.869449111723</v>
+        <v>993.3372728257399</v>
       </c>
       <c r="E90" t="n">
-        <v>1068.932284990714</v>
+        <v>1027.497472195187</v>
       </c>
       <c r="F90" t="n">
-        <v>1283100</v>
+        <v>1841900</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45961</v>
+        <v>45971</v>
       </c>
       <c r="B91" t="n">
-        <v>1055.529296875</v>
+        <v>1035.16064453125</v>
       </c>
       <c r="C91" t="n">
-        <v>1069.530258360293</v>
+        <v>1039.146669062118</v>
       </c>
       <c r="D91" t="n">
-        <v>1047.726696720774</v>
+        <v>1017.50252423211</v>
       </c>
       <c r="E91" t="n">
-        <v>1067.935872687321</v>
+        <v>1033.147682680151</v>
       </c>
       <c r="F91" t="n">
-        <v>1179400</v>
+        <v>992900</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45964</v>
+        <v>45972</v>
       </c>
       <c r="B92" t="n">
-        <v>1063.092651367188</v>
+        <v>1018.847839355469</v>
       </c>
       <c r="C92" t="n">
-        <v>1069.649739772258</v>
+        <v>1033.356967014897</v>
       </c>
       <c r="D92" t="n">
-        <v>1059.276076554389</v>
+        <v>1014.224096869386</v>
       </c>
       <c r="E92" t="n">
-        <v>1059.306000933798</v>
+        <v>1028.16520870322</v>
       </c>
       <c r="F92" t="n">
-        <v>868100</v>
+        <v>1026000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45965</v>
+        <v>45973</v>
       </c>
       <c r="B93" t="n">
-        <v>1026.540893554688</v>
+        <v>1033.705688476562</v>
       </c>
       <c r="C93" t="n">
-        <v>1059.545173457092</v>
+        <v>1035.070897046464</v>
       </c>
       <c r="D93" t="n">
-        <v>1025.23541206643</v>
+        <v>1021.647988300639</v>
       </c>
       <c r="E93" t="n">
-        <v>1046.281617777473</v>
+        <v>1026.560817179961</v>
       </c>
       <c r="F93" t="n">
-        <v>1735100</v>
+        <v>961900</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45966</v>
+        <v>45974</v>
       </c>
       <c r="B94" t="n">
-        <v>1040.103271484375</v>
+        <v>1016.296752929688</v>
       </c>
       <c r="C94" t="n">
-        <v>1046.96921330609</v>
+        <v>1038.219888345914</v>
       </c>
       <c r="D94" t="n">
-        <v>1027.198565779532</v>
+        <v>1005.982938551272</v>
       </c>
       <c r="E94" t="n">
-        <v>1027.497444631754</v>
+        <v>1037.352932856571</v>
       </c>
       <c r="F94" t="n">
-        <v>1169400</v>
+        <v>1406300</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45967</v>
+        <v>45975</v>
       </c>
       <c r="B95" t="n">
-        <v>1025.604125976562</v>
+        <v>1003.461730957031</v>
       </c>
       <c r="C95" t="n">
-        <v>1037.891125197865</v>
+        <v>1014.51301078443</v>
       </c>
       <c r="D95" t="n">
-        <v>1022.853759150235</v>
+        <v>977.5725209657202</v>
       </c>
       <c r="E95" t="n">
-        <v>1036.24686564937</v>
+        <v>985.8435097432505</v>
       </c>
       <c r="F95" t="n">
-        <v>1073000</v>
+        <v>1307800</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45968</v>
+        <v>45978</v>
       </c>
       <c r="B96" t="n">
-        <v>1013.406921386719</v>
+        <v>1016.436279296875</v>
       </c>
       <c r="C96" t="n">
-        <v>1031.782497319645</v>
+        <v>1021.418810077742</v>
       </c>
       <c r="D96" t="n">
-        <v>993.3372728257399</v>
+        <v>1000.761256923278</v>
       </c>
       <c r="E96" t="n">
-        <v>1027.497472195187</v>
+        <v>1001.209636036029</v>
       </c>
       <c r="F96" t="n">
-        <v>1841900</v>
+        <v>1691500</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45971</v>
+        <v>45979</v>
       </c>
       <c r="B97" t="n">
-        <v>1035.16064453125</v>
+        <v>1000.551940917969</v>
       </c>
       <c r="C97" t="n">
-        <v>1039.146669062118</v>
+        <v>1014.16418787122</v>
       </c>
       <c r="D97" t="n">
-        <v>1017.50252423211</v>
+        <v>990.5171169056545</v>
       </c>
       <c r="E97" t="n">
-        <v>1033.147682680151</v>
+        <v>1007.547433402833</v>
       </c>
       <c r="F97" t="n">
-        <v>992900</v>
+        <v>1414000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45972</v>
+        <v>45980</v>
       </c>
       <c r="B98" t="n">
-        <v>1018.847778320312</v>
+        <v>1035.69873046875</v>
       </c>
       <c r="C98" t="n">
-        <v>1033.356905110556</v>
+        <v>1041.079888201733</v>
       </c>
       <c r="D98" t="n">
-        <v>1014.22403611122</v>
+        <v>1001.488716896297</v>
       </c>
       <c r="E98" t="n">
-        <v>1028.165147109897</v>
+        <v>1002.256046122503</v>
       </c>
       <c r="F98" t="n">
-        <v>1026000</v>
+        <v>1587800</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45973</v>
+        <v>45981</v>
       </c>
       <c r="B99" t="n">
-        <v>1033.705810546875</v>
+        <v>977.6123657226562</v>
       </c>
       <c r="C99" t="n">
-        <v>1035.071019277994</v>
+        <v>1047.278083495809</v>
       </c>
       <c r="D99" t="n">
-        <v>1021.648108947058</v>
+        <v>973.5865027963351</v>
       </c>
       <c r="E99" t="n">
-        <v>1026.560938406536</v>
+        <v>1038.588579113678</v>
       </c>
       <c r="F99" t="n">
-        <v>961900</v>
+        <v>2055100</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45974</v>
+        <v>45982</v>
       </c>
       <c r="B100" t="n">
-        <v>1016.296752929688</v>
+        <v>963.1929321289062</v>
       </c>
       <c r="C100" t="n">
-        <v>1038.219888345914</v>
+        <v>975.1210812455514</v>
       </c>
       <c r="D100" t="n">
-        <v>1005.982938551272</v>
+        <v>942.8043949242191</v>
       </c>
       <c r="E100" t="n">
-        <v>1037.352932856571</v>
+        <v>959.9841507803837</v>
       </c>
       <c r="F100" t="n">
-        <v>1406300</v>
+        <v>2481800</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45975</v>
+        <v>45985</v>
       </c>
       <c r="B101" t="n">
-        <v>1003.461791992188</v>
+        <v>984.3687133789062</v>
       </c>
       <c r="C101" t="n">
-        <v>1014.513072491776</v>
+        <v>991.6631457028512</v>
       </c>
       <c r="D101" t="n">
-        <v>977.5725804261757</v>
+        <v>974.1744749171926</v>
       </c>
       <c r="E101" t="n">
-        <v>985.8435697067855</v>
+        <v>974.2043384743301</v>
       </c>
       <c r="F101" t="n">
-        <v>1307800</v>
+        <v>1628100</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45978</v>
+        <v>45986</v>
       </c>
       <c r="B102" t="n">
-        <v>1016.436279296875</v>
+        <v>999.71484375</v>
       </c>
       <c r="C102" t="n">
-        <v>1021.418810077742</v>
+        <v>1003.362090221281</v>
       </c>
       <c r="D102" t="n">
-        <v>1000.761256923278</v>
+        <v>970.3378627002569</v>
       </c>
       <c r="E102" t="n">
-        <v>1001.209636036029</v>
+        <v>990.3576974775409</v>
       </c>
       <c r="F102" t="n">
-        <v>1691500</v>
+        <v>1193000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45979</v>
+        <v>45987</v>
       </c>
       <c r="B103" t="n">
-        <v>1000.552001953125</v>
+        <v>1037.3330078125</v>
       </c>
       <c r="C103" t="n">
-        <v>1014.164249736743</v>
+        <v>1051.314018696411</v>
       </c>
       <c r="D103" t="n">
-        <v>990.5171773286714</v>
+        <v>1033.675907988132</v>
       </c>
       <c r="E103" t="n">
-        <v>1007.547494864725</v>
+        <v>1037.034128945135</v>
       </c>
       <c r="F103" t="n">
-        <v>1414000</v>
+        <v>1572400</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45980</v>
+        <v>45989</v>
       </c>
       <c r="B104" t="n">
-        <v>1035.69873046875</v>
+        <v>1056.296630859375</v>
       </c>
       <c r="C104" t="n">
-        <v>1041.079888201733</v>
+        <v>1056.575681805442</v>
       </c>
       <c r="D104" t="n">
-        <v>1001.488716896297</v>
+        <v>1031.822378834576</v>
       </c>
       <c r="E104" t="n">
-        <v>1002.256046122503</v>
+        <v>1036.765132579798</v>
       </c>
       <c r="F104" t="n">
-        <v>1587800</v>
+        <v>939700</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45981</v>
+        <v>45992</v>
       </c>
       <c r="B105" t="n">
-        <v>977.6123657226562</v>
+        <v>1084.188720703125</v>
       </c>
       <c r="C105" t="n">
-        <v>1047.278083495809</v>
+        <v>1087.487214461728</v>
       </c>
       <c r="D105" t="n">
-        <v>973.5865027963351</v>
+        <v>1050.785814959754</v>
       </c>
       <c r="E105" t="n">
-        <v>1038.588579113678</v>
+        <v>1052.340422948947</v>
       </c>
       <c r="F105" t="n">
-        <v>2055100</v>
+        <v>2103100</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45982</v>
+        <v>45993</v>
       </c>
       <c r="B106" t="n">
-        <v>963.1929931640625</v>
+        <v>1104.906127929688</v>
       </c>
       <c r="C106" t="n">
-        <v>975.1211430365649</v>
+        <v>1109.320582092557</v>
       </c>
       <c r="D106" t="n">
-        <v>942.804454667404</v>
+        <v>1084.876378466917</v>
       </c>
       <c r="E106" t="n">
-        <v>959.9842116122073</v>
+        <v>1085.803061074047</v>
       </c>
       <c r="F106" t="n">
-        <v>2481800</v>
+        <v>1426000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45985</v>
+        <v>45994</v>
       </c>
       <c r="B107" t="n">
-        <v>984.3687133789062</v>
+        <v>1136.933837890625</v>
       </c>
       <c r="C107" t="n">
-        <v>991.6631457028512</v>
+        <v>1137.73096982254</v>
       </c>
       <c r="D107" t="n">
-        <v>974.1744749171926</v>
+        <v>1101.757122217278</v>
       </c>
       <c r="E107" t="n">
-        <v>974.2043384743301</v>
+        <v>1106.360975754163</v>
       </c>
       <c r="F107" t="n">
-        <v>1628100</v>
+        <v>2059500</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45986</v>
+        <v>45995</v>
       </c>
       <c r="B108" t="n">
-        <v>999.7149047851562</v>
+        <v>1106.201538085938</v>
       </c>
       <c r="C108" t="n">
-        <v>1003.362151479111</v>
+        <v>1125.593631094292</v>
       </c>
       <c r="D108" t="n">
-        <v>970.3379219418731</v>
+        <v>1098.319261774406</v>
       </c>
       <c r="E108" t="n">
-        <v>990.3577579414194</v>
+        <v>1118.608113030988</v>
       </c>
       <c r="F108" t="n">
-        <v>1193000</v>
+        <v>1511800</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45987</v>
+        <v>45996</v>
       </c>
       <c r="B109" t="n">
-        <v>1037.3330078125</v>
+        <v>1095.628662109375</v>
       </c>
       <c r="C109" t="n">
-        <v>1051.314018696411</v>
+        <v>1125.43419714457</v>
       </c>
       <c r="D109" t="n">
-        <v>1033.675907988132</v>
+        <v>1094.42292851184</v>
       </c>
       <c r="E109" t="n">
-        <v>1037.034128945135</v>
+        <v>1118.010274479359</v>
       </c>
       <c r="F109" t="n">
-        <v>1572400</v>
+        <v>1054400</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>45989</v>
+        <v>45999</v>
       </c>
       <c r="B110" t="n">
-        <v>1056.296508789062</v>
+        <v>1115.77783203125</v>
       </c>
       <c r="C110" t="n">
-        <v>1056.575559702881</v>
+        <v>1130.217317013055</v>
       </c>
       <c r="D110" t="n">
-        <v>1031.822259592616</v>
+        <v>1110.137695213593</v>
       </c>
       <c r="E110" t="n">
-        <v>1036.765012766632</v>
+        <v>1114.910876609186</v>
       </c>
       <c r="F110" t="n">
-        <v>939700</v>
+        <v>1118800</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="B111" t="n">
-        <v>1084.188720703125</v>
+        <v>1107.556640625</v>
       </c>
       <c r="C111" t="n">
-        <v>1087.487214461728</v>
+        <v>1111.841665354789</v>
       </c>
       <c r="D111" t="n">
-        <v>1050.785814959754</v>
+        <v>1101.747054067627</v>
       </c>
       <c r="E111" t="n">
-        <v>1052.340422948947</v>
+        <v>1104.029091878643</v>
       </c>
       <c r="F111" t="n">
-        <v>2103100</v>
+        <v>904700</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>45993</v>
+        <v>46001</v>
       </c>
       <c r="B112" t="n">
-        <v>1104.906127929688</v>
+        <v>1115.4091796875</v>
       </c>
       <c r="C112" t="n">
-        <v>1109.320582092557</v>
+        <v>1120.032982693879</v>
       </c>
       <c r="D112" t="n">
-        <v>1084.876378466917</v>
+        <v>1095.040652929452</v>
       </c>
       <c r="E112" t="n">
-        <v>1085.803061074047</v>
+        <v>1105.523916802798</v>
       </c>
       <c r="F112" t="n">
-        <v>1426000</v>
+        <v>1093600</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>45994</v>
+        <v>46002</v>
       </c>
       <c r="B113" t="n">
-        <v>1136.933837890625</v>
+        <v>1118.916870117188</v>
       </c>
       <c r="C113" t="n">
-        <v>1137.73096982254</v>
+        <v>1123.809749105949</v>
       </c>
       <c r="D113" t="n">
-        <v>1101.757122217278</v>
+        <v>1091.64250315139</v>
       </c>
       <c r="E113" t="n">
-        <v>1106.360975754163</v>
+        <v>1110.855169865535</v>
       </c>
       <c r="F113" t="n">
-        <v>2059500</v>
+        <v>1403600</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>45995</v>
+        <v>46003</v>
       </c>
       <c r="B114" t="n">
-        <v>1106.201538085938</v>
+        <v>1077.07373046875</v>
       </c>
       <c r="C114" t="n">
-        <v>1125.593631094292</v>
+        <v>1110.66603807828</v>
       </c>
       <c r="D114" t="n">
-        <v>1098.319261774406</v>
+        <v>1073.426483619878</v>
       </c>
       <c r="E114" t="n">
-        <v>1118.608113030988</v>
+        <v>1105.514057096048</v>
       </c>
       <c r="F114" t="n">
-        <v>1511800</v>
+        <v>1623000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>45996</v>
+        <v>46006</v>
       </c>
       <c r="B115" t="n">
-        <v>1095.628540039062</v>
+        <v>1084.019287109375</v>
       </c>
       <c r="C115" t="n">
-        <v>1125.434071753451</v>
+        <v>1093.874747716871</v>
       </c>
       <c r="D115" t="n">
-        <v>1094.422806575865</v>
+        <v>1075.818060802492</v>
       </c>
       <c r="E115" t="n">
-        <v>1118.010149915382</v>
+        <v>1085.54397074228</v>
       </c>
       <c r="F115" t="n">
-        <v>1054400</v>
+        <v>1283400</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>45999</v>
+        <v>46007</v>
       </c>
       <c r="B116" t="n">
-        <v>1115.777954101562</v>
+        <v>1072.29052734375</v>
       </c>
       <c r="C116" t="n">
-        <v>1130.217440663102</v>
+        <v>1084.258576338321</v>
       </c>
       <c r="D116" t="n">
-        <v>1110.137816666853</v>
+        <v>1062.21574278265</v>
       </c>
       <c r="E116" t="n">
-        <v>1114.91099858465</v>
+        <v>1077.751361765967</v>
       </c>
       <c r="F116" t="n">
-        <v>1118800</v>
+        <v>956300</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="B117" t="n">
-        <v>1107.556762695312</v>
+        <v>1011.882263183594</v>
       </c>
       <c r="C117" t="n">
-        <v>1111.84178789738</v>
+        <v>1061.398657706778</v>
       </c>
       <c r="D117" t="n">
-        <v>1101.747175497631</v>
+        <v>1006.481216717462</v>
       </c>
       <c r="E117" t="n">
-        <v>1104.029213560164</v>
+        <v>1057.063880152008</v>
       </c>
       <c r="F117" t="n">
-        <v>904700</v>
+        <v>2140900</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46001</v>
+        <v>46009</v>
       </c>
       <c r="B118" t="n">
-        <v>1115.409301757812</v>
+        <v>1032.689331054688</v>
       </c>
       <c r="C118" t="n">
-        <v>1120.033105270221</v>
+        <v>1048.135176145749</v>
       </c>
       <c r="D118" t="n">
-        <v>1095.040772770634</v>
+        <v>1031.533349877927</v>
       </c>
       <c r="E118" t="n">
-        <v>1105.524037791268</v>
+        <v>1044.308505004158</v>
       </c>
       <c r="F118" t="n">
-        <v>1093600</v>
+        <v>1645400</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46002</v>
+        <v>46010</v>
       </c>
       <c r="B119" t="n">
-        <v>1118.9169921875</v>
+        <v>1052.330444335938</v>
       </c>
       <c r="C119" t="n">
-        <v>1123.80987171006</v>
+        <v>1058.967209357413</v>
       </c>
       <c r="D119" t="n">
-        <v>1091.642622246155</v>
+        <v>1038.917510478499</v>
       </c>
       <c r="E119" t="n">
-        <v>1110.855291056341</v>
+        <v>1038.917510478499</v>
       </c>
       <c r="F119" t="n">
-        <v>1403600</v>
+        <v>2319600</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46003</v>
+        <v>46013</v>
       </c>
       <c r="B120" t="n">
-        <v>1077.07373046875</v>
+        <v>1053.287109375</v>
       </c>
       <c r="C120" t="n">
-        <v>1110.66603807828</v>
+        <v>1063.431596067851</v>
       </c>
       <c r="D120" t="n">
-        <v>1073.426483619878</v>
+        <v>1046.331515525282</v>
       </c>
       <c r="E120" t="n">
-        <v>1105.514057096048</v>
+        <v>1062.275614809477</v>
       </c>
       <c r="F120" t="n">
-        <v>1623000</v>
+        <v>703700</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46006</v>
+        <v>46014</v>
       </c>
       <c r="B121" t="n">
-        <v>1084.019287109375</v>
+        <v>1058.130126953125</v>
       </c>
       <c r="C121" t="n">
-        <v>1093.874747716871</v>
+        <v>1061.029994103644</v>
       </c>
       <c r="D121" t="n">
-        <v>1075.818060802492</v>
+        <v>1052.001589392392</v>
       </c>
       <c r="E121" t="n">
-        <v>1085.54397074228</v>
+        <v>1054.243728379698</v>
       </c>
       <c r="F121" t="n">
-        <v>1283400</v>
+        <v>543600</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46007</v>
+        <v>46015</v>
       </c>
       <c r="B122" t="n">
-        <v>1072.29052734375</v>
+        <v>1061.797241210938</v>
       </c>
       <c r="C122" t="n">
-        <v>1084.258576338321</v>
+        <v>1063.072798263999</v>
       </c>
       <c r="D122" t="n">
-        <v>1062.21574278265</v>
+        <v>1053.745393751827</v>
       </c>
       <c r="E122" t="n">
-        <v>1077.751361765967</v>
+        <v>1056.117083229563</v>
       </c>
       <c r="F122" t="n">
-        <v>956300</v>
+        <v>229800</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46008</v>
+        <v>46017</v>
       </c>
       <c r="B123" t="n">
-        <v>1011.882263183594</v>
+        <v>1069.001953125</v>
       </c>
       <c r="C123" t="n">
-        <v>1061.398657706778</v>
+        <v>1072.33024954568</v>
       </c>
       <c r="D123" t="n">
-        <v>1006.481216717462</v>
+        <v>1059.365695036588</v>
       </c>
       <c r="E123" t="n">
-        <v>1057.063880152008</v>
+        <v>1062.524663266867</v>
       </c>
       <c r="F123" t="n">
-        <v>2140900</v>
+        <v>363800</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46009</v>
+        <v>46020</v>
       </c>
       <c r="B124" t="n">
-        <v>1032.689453125</v>
+        <v>1062.275634765625</v>
       </c>
       <c r="C124" t="n">
-        <v>1048.135300041856</v>
+        <v>1069.898931707858</v>
       </c>
       <c r="D124" t="n">
-        <v>1031.533471811595</v>
+        <v>1057.362805558106</v>
       </c>
       <c r="E124" t="n">
-        <v>1044.308628447929</v>
+        <v>1060.860552135792</v>
       </c>
       <c r="F124" t="n">
-        <v>1645400</v>
+        <v>424300</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46010</v>
+        <v>46021</v>
       </c>
       <c r="B125" t="n">
-        <v>1052.330444335938</v>
+        <v>1068.394165039062</v>
       </c>
       <c r="C125" t="n">
-        <v>1058.967209357413</v>
+        <v>1082.265575046212</v>
       </c>
       <c r="D125" t="n">
-        <v>1038.917510478499</v>
+        <v>1066.680203580531</v>
       </c>
       <c r="E125" t="n">
-        <v>1038.917510478499</v>
+        <v>1080.790643698824</v>
       </c>
       <c r="F125" t="n">
-        <v>2319600</v>
+        <v>807300</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46013</v>
+        <v>46022</v>
       </c>
       <c r="B126" t="n">
-        <v>1053.287109375</v>
+        <v>1066.1220703125</v>
       </c>
       <c r="C126" t="n">
-        <v>1063.431596067851</v>
+        <v>1076.764809670222</v>
       </c>
       <c r="D126" t="n">
-        <v>1046.331515525282</v>
+        <v>1065.185412907116</v>
       </c>
       <c r="E126" t="n">
-        <v>1062.275614809477</v>
+        <v>1076.455834370264</v>
       </c>
       <c r="F126" t="n">
-        <v>703700</v>
+        <v>561300</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46014</v>
+        <v>46024</v>
       </c>
       <c r="B127" t="n">
-        <v>1058.130126953125</v>
+        <v>1159.713989257812</v>
       </c>
       <c r="C127" t="n">
-        <v>1061.029994103644</v>
+        <v>1168.672570068307</v>
       </c>
       <c r="D127" t="n">
-        <v>1052.001589392392</v>
+        <v>1129.519803400884</v>
       </c>
       <c r="E127" t="n">
-        <v>1054.243728379698</v>
+        <v>1129.798854325297</v>
       </c>
       <c r="F127" t="n">
-        <v>543600</v>
+        <v>2697900</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46015</v>
+        <v>46027</v>
       </c>
       <c r="B128" t="n">
-        <v>1061.797241210938</v>
+        <v>1223.89892578125</v>
       </c>
       <c r="C128" t="n">
-        <v>1063.072798263999</v>
+        <v>1233.535184797811</v>
       </c>
       <c r="D128" t="n">
-        <v>1053.745393751827</v>
+        <v>1206.988244286567</v>
       </c>
       <c r="E128" t="n">
-        <v>1056.117083229563</v>
+        <v>1206.988244286567</v>
       </c>
       <c r="F128" t="n">
-        <v>229800</v>
+        <v>3290600</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46017</v>
+        <v>46028</v>
       </c>
       <c r="B129" t="n">
-        <v>1069.001953125</v>
+        <v>1237.849975585938</v>
       </c>
       <c r="C129" t="n">
-        <v>1072.33024954568</v>
+        <v>1242.025399809945</v>
       </c>
       <c r="D129" t="n">
-        <v>1059.365695036588</v>
+        <v>1218.149150234177</v>
       </c>
       <c r="E129" t="n">
-        <v>1062.524663266867</v>
+        <v>1218.547655398281</v>
       </c>
       <c r="F129" t="n">
-        <v>363800</v>
+        <v>1895800</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46020</v>
+        <v>46029</v>
       </c>
       <c r="B130" t="n">
-        <v>1062.275634765625</v>
+        <v>1224.177978515625</v>
       </c>
       <c r="C130" t="n">
-        <v>1069.898931707858</v>
+        <v>1231.442547854445</v>
       </c>
       <c r="D130" t="n">
-        <v>1057.362805558106</v>
+        <v>1217.730612405509</v>
       </c>
       <c r="E130" t="n">
-        <v>1060.860552135792</v>
+        <v>1223.161522698559</v>
       </c>
       <c r="F130" t="n">
-        <v>424300</v>
+        <v>1351200</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46021</v>
+        <v>46030</v>
       </c>
       <c r="B131" t="n">
-        <v>1068.394165039062</v>
+        <v>1190.147216796875</v>
       </c>
       <c r="C131" t="n">
-        <v>1082.265575046212</v>
+        <v>1220.2617262442</v>
       </c>
       <c r="D131" t="n">
-        <v>1066.680203580531</v>
+        <v>1171.891276958021</v>
       </c>
       <c r="E131" t="n">
-        <v>1080.790643698824</v>
+        <v>1213.007132001847</v>
       </c>
       <c r="F131" t="n">
-        <v>807300</v>
+        <v>1682300</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46022</v>
+        <v>46031</v>
       </c>
       <c r="B132" t="n">
-        <v>1066.1220703125</v>
+        <v>1269.429321289062</v>
       </c>
       <c r="C132" t="n">
-        <v>1076.764809670222</v>
+        <v>1277.520946756903</v>
       </c>
       <c r="D132" t="n">
-        <v>1065.185412907116</v>
+        <v>1216.724093841591</v>
       </c>
       <c r="E132" t="n">
-        <v>1076.455834370264</v>
+        <v>1228.542642761132</v>
       </c>
       <c r="F132" t="n">
-        <v>561300</v>
+        <v>2394500</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46024</v>
+        <v>46034</v>
       </c>
       <c r="B133" t="n">
-        <v>1159.713989257812</v>
+        <v>1276.753540039062</v>
       </c>
       <c r="C133" t="n">
-        <v>1168.672570068307</v>
+        <v>1279.075477193212</v>
       </c>
       <c r="D133" t="n">
-        <v>1129.519803400884</v>
+        <v>1250.8643300305</v>
       </c>
       <c r="E133" t="n">
-        <v>1129.798854325297</v>
+        <v>1251.671558391509</v>
       </c>
       <c r="F133" t="n">
-        <v>2697900</v>
+        <v>1488600</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46027</v>
+        <v>46035</v>
       </c>
       <c r="B134" t="n">
-        <v>1223.898803710938</v>
+        <v>1265.722290039062</v>
       </c>
       <c r="C134" t="n">
-        <v>1233.535061766389</v>
+        <v>1286.967747709229</v>
       </c>
       <c r="D134" t="n">
-        <v>1206.988123902908</v>
+        <v>1263.689378559822</v>
       </c>
       <c r="E134" t="n">
-        <v>1206.988123902908</v>
+        <v>1277.839717282545</v>
       </c>
       <c r="F134" t="n">
-        <v>3290600</v>
+        <v>1374200</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46028</v>
+        <v>46036</v>
       </c>
       <c r="B135" t="n">
-        <v>1237.849975585938</v>
+        <v>1259.3046875</v>
       </c>
       <c r="C135" t="n">
-        <v>1242.025399809945</v>
+        <v>1268.821369624142</v>
       </c>
       <c r="D135" t="n">
-        <v>1218.149150234177</v>
+        <v>1245.253975506324</v>
       </c>
       <c r="E135" t="n">
-        <v>1218.547655398281</v>
+        <v>1262.692832644103</v>
       </c>
       <c r="F135" t="n">
-        <v>1895800</v>
+        <v>1536500</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46029</v>
+        <v>46037</v>
       </c>
       <c r="B136" t="n">
-        <v>1224.177856445312</v>
+        <v>1326.947631835938</v>
       </c>
       <c r="C136" t="n">
-        <v>1231.442425059738</v>
+        <v>1353.255419849553</v>
       </c>
       <c r="D136" t="n">
-        <v>1217.730490978103</v>
+        <v>1325.353246244408</v>
       </c>
       <c r="E136" t="n">
-        <v>1223.161400729604</v>
+        <v>1348.910667414011</v>
       </c>
       <c r="F136" t="n">
-        <v>1351200</v>
+        <v>2858400</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46030</v>
+        <v>46038</v>
       </c>
       <c r="B137" t="n">
-        <v>1190.147216796875</v>
+        <v>1353.823364257812</v>
       </c>
       <c r="C137" t="n">
-        <v>1220.2617262442</v>
+        <v>1370.564716947318</v>
       </c>
       <c r="D137" t="n">
-        <v>1171.891276958021</v>
+        <v>1333.564437158512</v>
       </c>
       <c r="E137" t="n">
-        <v>1213.007132001847</v>
+        <v>1350.973371144866</v>
       </c>
       <c r="F137" t="n">
-        <v>1682300</v>
+        <v>2469100</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46031</v>
+        <v>46042</v>
       </c>
       <c r="B138" t="n">
-        <v>1269.429321289062</v>
+        <v>1321.436889648438</v>
       </c>
       <c r="C138" t="n">
-        <v>1277.520946756903</v>
+        <v>1346.538943445575</v>
       </c>
       <c r="D138" t="n">
-        <v>1216.724093841591</v>
+        <v>1306.728570421208</v>
       </c>
       <c r="E138" t="n">
-        <v>1228.542642761132</v>
+        <v>1314.511220391343</v>
       </c>
       <c r="F138" t="n">
-        <v>2394500</v>
+        <v>2970800</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46034</v>
+        <v>46043</v>
       </c>
       <c r="B139" t="n">
-        <v>1276.753540039062</v>
+        <v>1355.338012695312</v>
       </c>
       <c r="C139" t="n">
-        <v>1279.075477193212</v>
+        <v>1366.209928829638</v>
       </c>
       <c r="D139" t="n">
-        <v>1250.8643300305</v>
+        <v>1318.048830491334</v>
       </c>
       <c r="E139" t="n">
-        <v>1251.671558391509</v>
+        <v>1327.346189059867</v>
       </c>
       <c r="F139" t="n">
-        <v>1488600</v>
+        <v>2387200</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46035</v>
+        <v>46044</v>
       </c>
       <c r="B140" t="n">
-        <v>1265.722412109375</v>
+        <v>1390.126098632812</v>
       </c>
       <c r="C140" t="n">
-        <v>1286.967871828522</v>
+        <v>1393.912870713139</v>
       </c>
       <c r="D140" t="n">
-        <v>1263.689500434074</v>
+        <v>1368.482013947541</v>
       </c>
       <c r="E140" t="n">
-        <v>1277.839840521501</v>
+        <v>1388.780839640319</v>
       </c>
       <c r="F140" t="n">
-        <v>1374200</v>
+        <v>1844200</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46036</v>
+        <v>46045</v>
       </c>
       <c r="B141" t="n">
-        <v>1259.304809570312</v>
+        <v>1384.18701171875</v>
       </c>
       <c r="C141" t="n">
-        <v>1268.821492616951</v>
+        <v>1388.491864981784</v>
       </c>
       <c r="D141" t="n">
-        <v>1245.254096214635</v>
+        <v>1358.507027467922</v>
       </c>
       <c r="E141" t="n">
-        <v>1262.692955042844</v>
+        <v>1371.511360398625</v>
       </c>
       <c r="F141" t="n">
-        <v>1536500</v>
+        <v>1556300</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46037</v>
+        <v>46048</v>
       </c>
       <c r="B142" t="n">
-        <v>1326.947631835938</v>
+        <v>1408.411987304688</v>
       </c>
       <c r="C142" t="n">
-        <v>1353.255419849553</v>
+        <v>1414.988903773872</v>
       </c>
       <c r="D142" t="n">
-        <v>1325.353246244408</v>
+        <v>1380.320536437029</v>
       </c>
       <c r="E142" t="n">
-        <v>1348.910667414011</v>
+        <v>1381.028016899876</v>
       </c>
       <c r="F142" t="n">
-        <v>2858400</v>
+        <v>2001300</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46038</v>
+        <v>46049</v>
       </c>
       <c r="B143" t="n">
-        <v>1353.823364257812</v>
+        <v>1449.5078125</v>
       </c>
       <c r="C143" t="n">
-        <v>1370.564716947318</v>
+        <v>1468.441428903691</v>
       </c>
       <c r="D143" t="n">
-        <v>1333.564437158512</v>
+        <v>1412.049181264755</v>
       </c>
       <c r="E143" t="n">
-        <v>1350.973371144866</v>
+        <v>1412.676984990209</v>
       </c>
       <c r="F143" t="n">
-        <v>2469100</v>
+        <v>3473900</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46042</v>
+        <v>46050</v>
       </c>
       <c r="B144" t="n">
-        <v>1321.436889648438</v>
+        <v>1417.948608398438</v>
       </c>
       <c r="C144" t="n">
-        <v>1346.538943445575</v>
+        <v>1488.262020756227</v>
       </c>
       <c r="D144" t="n">
-        <v>1306.728570421208</v>
+        <v>1403.13056646205</v>
       </c>
       <c r="E144" t="n">
-        <v>1314.511220391343</v>
+        <v>1487.783717255887</v>
       </c>
       <c r="F144" t="n">
-        <v>2970800</v>
+        <v>5036800</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46043</v>
+        <v>46051</v>
       </c>
       <c r="B145" t="n">
-        <v>1355.338012695312</v>
+        <v>1450.075927734375</v>
       </c>
       <c r="C145" t="n">
-        <v>1366.209928829638</v>
+        <v>1462.362804809723</v>
       </c>
       <c r="D145" t="n">
-        <v>1318.048830491334</v>
+        <v>1394.201759612252</v>
       </c>
       <c r="E145" t="n">
-        <v>1327.346189059867</v>
+        <v>1454.22130574752</v>
       </c>
       <c r="F145" t="n">
-        <v>2387200</v>
+        <v>2818900</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46044</v>
+        <v>46052</v>
       </c>
       <c r="B146" t="n">
-        <v>1390.126098632812</v>
+        <v>1418.028198242188</v>
       </c>
       <c r="C146" t="n">
-        <v>1393.912870713139</v>
+        <v>1461.306512236061</v>
       </c>
       <c r="D146" t="n">
-        <v>1368.482013947541</v>
+        <v>1411.062630246558</v>
       </c>
       <c r="E146" t="n">
-        <v>1388.780839640319</v>
+        <v>1435.00870132706</v>
       </c>
       <c r="F146" t="n">
-        <v>1844200</v>
+        <v>2358800</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46045</v>
+        <v>46055</v>
       </c>
       <c r="B147" t="n">
-        <v>1384.18701171875</v>
+        <v>1436.35400390625</v>
       </c>
       <c r="C147" t="n">
-        <v>1388.491864981784</v>
+        <v>1448.082900671148</v>
       </c>
       <c r="D147" t="n">
-        <v>1358.507027467922</v>
+        <v>1390.524696125964</v>
       </c>
       <c r="E147" t="n">
-        <v>1371.511360398625</v>
+        <v>1392.358233368624</v>
       </c>
       <c r="F147" t="n">
-        <v>1556300</v>
+        <v>1766600</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46048</v>
+        <v>46056</v>
       </c>
       <c r="B148" t="n">
-        <v>1408.411987304688</v>
+        <v>1391.003051757812</v>
       </c>
       <c r="C148" t="n">
-        <v>1414.988903773872</v>
+        <v>1440.758658861144</v>
       </c>
       <c r="D148" t="n">
-        <v>1380.320536437029</v>
+        <v>1367.116827811657</v>
       </c>
       <c r="E148" t="n">
-        <v>1381.028016899876</v>
+        <v>1431.022774017057</v>
       </c>
       <c r="F148" t="n">
-        <v>2001300</v>
+        <v>2205100</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46049</v>
+        <v>46057</v>
       </c>
       <c r="B149" t="n">
-        <v>1449.507934570312</v>
+        <v>1334.451293945312</v>
       </c>
       <c r="C149" t="n">
-        <v>1468.441552568498</v>
+        <v>1401.187282037884</v>
       </c>
       <c r="D149" t="n">
-        <v>1412.049300180488</v>
+        <v>1311.461950442863</v>
       </c>
       <c r="E149" t="n">
-        <v>1412.677103958813</v>
+        <v>1390.883442442061</v>
       </c>
       <c r="F149" t="n">
-        <v>3473900</v>
+        <v>2479400</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46050</v>
+        <v>46058</v>
       </c>
       <c r="B150" t="n">
-        <v>1417.948608398438</v>
+        <v>1345.442749023438</v>
       </c>
       <c r="C150" t="n">
-        <v>1488.262020756227</v>
+        <v>1364.077364975892</v>
       </c>
       <c r="D150" t="n">
-        <v>1403.13056646205</v>
+        <v>1314.919761430214</v>
       </c>
       <c r="E150" t="n">
-        <v>1487.783717255887</v>
+        <v>1324.476221145867</v>
       </c>
       <c r="F150" t="n">
-        <v>5036800</v>
+        <v>1790200</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46051</v>
+        <v>46059</v>
       </c>
       <c r="B151" t="n">
-        <v>1450.076049804688</v>
+        <v>1408.073120117188</v>
       </c>
       <c r="C151" t="n">
-        <v>1462.36292791437</v>
+        <v>1411.022739301684</v>
       </c>
       <c r="D151" t="n">
-        <v>1394.201876978964</v>
+        <v>1363.73857264028</v>
       </c>
       <c r="E151" t="n">
-        <v>1454.221428166799</v>
+        <v>1367.575096867426</v>
       </c>
       <c r="F151" t="n">
-        <v>2818900</v>
+        <v>1971000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46052</v>
+        <v>46062</v>
       </c>
       <c r="B152" t="n">
-        <v>1418.0283203125</v>
+        <v>1424.49560546875</v>
       </c>
       <c r="C152" t="n">
-        <v>1461.306638031968</v>
+        <v>1432.069028086465</v>
       </c>
       <c r="D152" t="n">
-        <v>1411.062751717242</v>
+        <v>1403.678576830447</v>
       </c>
       <c r="E152" t="n">
-        <v>1435.008824859131</v>
+        <v>1410.893271821639</v>
       </c>
       <c r="F152" t="n">
-        <v>2358800</v>
+        <v>1125100</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46055</v>
+        <v>46063</v>
       </c>
       <c r="B153" t="n">
-        <v>1436.35400390625</v>
+        <v>1410.5390625</v>
       </c>
       <c r="C153" t="n">
-        <v>1448.082900671148</v>
+        <v>1436.751827493038</v>
       </c>
       <c r="D153" t="n">
-        <v>1390.524696125964</v>
+        <v>1407.725262179819</v>
       </c>
       <c r="E153" t="n">
-        <v>1392.358233368624</v>
+        <v>1436.133183632331</v>
       </c>
       <c r="F153" t="n">
-        <v>1766600</v>
+        <v>1200600</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46056</v>
+        <v>46064</v>
       </c>
       <c r="B154" t="n">
-        <v>1391.003051757812</v>
+        <v>1432.501098632812</v>
       </c>
       <c r="C154" t="n">
-        <v>1440.758658861144</v>
+        <v>1448.326517691443</v>
       </c>
       <c r="D154" t="n">
-        <v>1367.116827811657</v>
+        <v>1406.268357806805</v>
       </c>
       <c r="E154" t="n">
-        <v>1431.022774017057</v>
+        <v>1437.26072207045</v>
       </c>
       <c r="F154" t="n">
-        <v>2205100</v>
+        <v>1139300</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46057</v>
+        <v>46065</v>
       </c>
       <c r="B155" t="n">
-        <v>1334.451293945312</v>
+        <v>1403.803833007812</v>
       </c>
       <c r="C155" t="n">
-        <v>1401.187282037884</v>
+        <v>1436.113268225754</v>
       </c>
       <c r="D155" t="n">
-        <v>1311.461950442863</v>
+        <v>1389.165761265365</v>
       </c>
       <c r="E155" t="n">
-        <v>1390.883442442061</v>
+        <v>1432.10201000977</v>
       </c>
       <c r="F155" t="n">
-        <v>2479400</v>
+        <v>1518100</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46058</v>
+        <v>46066</v>
       </c>
       <c r="B156" t="n">
-        <v>1345.442749023438</v>
+        <v>1403.544311523438</v>
       </c>
       <c r="C156" t="n">
-        <v>1364.077364975892</v>
+        <v>1433.528866967337</v>
       </c>
       <c r="D156" t="n">
-        <v>1314.919761430214</v>
+        <v>1397.946553004791</v>
       </c>
       <c r="E156" t="n">
-        <v>1324.476221145867</v>
+        <v>1411.766342890274</v>
       </c>
       <c r="F156" t="n">
-        <v>1790200</v>
+        <v>1248900</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46059</v>
+        <v>46070</v>
       </c>
       <c r="B157" t="n">
-        <v>1408.073120117188</v>
+        <v>1416.685668945312</v>
       </c>
       <c r="C157" t="n">
-        <v>1411.022739301684</v>
+        <v>1425.386634780744</v>
       </c>
       <c r="D157" t="n">
-        <v>1363.73857264028</v>
+        <v>1379.736345287416</v>
       </c>
       <c r="E157" t="n">
-        <v>1367.575096867426</v>
+        <v>1389.534889350905</v>
       </c>
       <c r="F157" t="n">
-        <v>1971000</v>
+        <v>1097200</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46062</v>
+        <v>46071</v>
       </c>
       <c r="B158" t="n">
-        <v>1424.49560546875</v>
+        <v>1465.518920898438</v>
       </c>
       <c r="C158" t="n">
-        <v>1432.069028086465</v>
+        <v>1473.281993755856</v>
       </c>
       <c r="D158" t="n">
-        <v>1403.678576830447</v>
+        <v>1424.269054819501</v>
       </c>
       <c r="E158" t="n">
-        <v>1410.893271821639</v>
+        <v>1433.339209216334</v>
       </c>
       <c r="F158" t="n">
-        <v>1125100</v>
+        <v>1334400</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46063</v>
+        <v>46072</v>
       </c>
       <c r="B159" t="n">
-        <v>1410.5390625</v>
+        <v>1455.750366210938</v>
       </c>
       <c r="C159" t="n">
-        <v>1436.751827493038</v>
+        <v>1456.608477254225</v>
       </c>
       <c r="D159" t="n">
-        <v>1407.725262179819</v>
+        <v>1424.468595006246</v>
       </c>
       <c r="E159" t="n">
-        <v>1436.133183632331</v>
+        <v>1435.903701160235</v>
       </c>
       <c r="F159" t="n">
-        <v>1200600</v>
+        <v>1135200</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46064</v>
+        <v>46073</v>
       </c>
       <c r="B160" t="n">
-        <v>1432.501098632812</v>
+        <v>1466.387084960938</v>
       </c>
       <c r="C160" t="n">
-        <v>1448.326517691443</v>
+        <v>1483.769162992887</v>
       </c>
       <c r="D160" t="n">
-        <v>1406.268357806805</v>
+        <v>1445.163422127828</v>
       </c>
       <c r="E160" t="n">
-        <v>1437.26072207045</v>
+        <v>1446.26112218896</v>
       </c>
       <c r="F160" t="n">
-        <v>1139300</v>
+        <v>1102500</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46065</v>
+        <v>46076</v>
       </c>
       <c r="B161" t="n">
-        <v>1403.803833007812</v>
+        <v>1482.751342773438</v>
       </c>
       <c r="C161" t="n">
-        <v>1436.113268225754</v>
+        <v>1489.756062492051</v>
       </c>
       <c r="D161" t="n">
-        <v>1389.165761265365</v>
+        <v>1458.813637629454</v>
       </c>
       <c r="E161" t="n">
-        <v>1432.10201000977</v>
+        <v>1468.193175118705</v>
       </c>
       <c r="F161" t="n">
-        <v>1518100</v>
+        <v>1284200</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="B162" t="n">
-        <v>1403.544311523438</v>
+        <v>1494.53564453125</v>
       </c>
       <c r="C162" t="n">
-        <v>1433.528866967337</v>
+        <v>1504.064757548291</v>
       </c>
       <c r="D162" t="n">
-        <v>1397.946553004791</v>
+        <v>1470.71767325709</v>
       </c>
       <c r="E162" t="n">
-        <v>1411.766342890274</v>
+        <v>1496.750776883683</v>
       </c>
       <c r="F162" t="n">
-        <v>1248900</v>
+        <v>1538900</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46070</v>
+        <v>46078</v>
       </c>
       <c r="B163" t="n">
-        <v>1416.685668945312</v>
+        <v>1523.18310546875</v>
       </c>
       <c r="C163" t="n">
-        <v>1425.386634780744</v>
+        <v>1543.847930732333</v>
       </c>
       <c r="D163" t="n">
-        <v>1379.736345287416</v>
+        <v>1513.174935804208</v>
       </c>
       <c r="E163" t="n">
-        <v>1389.534889350905</v>
+        <v>1519.082077495677</v>
       </c>
       <c r="F163" t="n">
-        <v>1097200</v>
+        <v>1306900</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46071</v>
+        <v>46079</v>
       </c>
       <c r="B164" t="n">
-        <v>1465.518920898438</v>
+        <v>1460.609741210938</v>
       </c>
       <c r="C164" t="n">
-        <v>1473.281993755856</v>
+        <v>1511.029520043906</v>
       </c>
       <c r="D164" t="n">
-        <v>1424.269054819501</v>
+        <v>1423.480756445574</v>
       </c>
       <c r="E164" t="n">
-        <v>1433.339209216334</v>
+        <v>1509.522801298568</v>
       </c>
       <c r="F164" t="n">
-        <v>1334400</v>
+        <v>2177900</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46072</v>
+        <v>46080</v>
       </c>
       <c r="B165" t="n">
-        <v>1455.750366210938</v>
+        <v>1447.398681640625</v>
       </c>
       <c r="C165" t="n">
-        <v>1456.608477254225</v>
+        <v>1458.534271634737</v>
       </c>
       <c r="D165" t="n">
-        <v>1424.468595006246</v>
+        <v>1421.395418812171</v>
       </c>
       <c r="E165" t="n">
-        <v>1435.903701160235</v>
+        <v>1427.222656904843</v>
       </c>
       <c r="F165" t="n">
-        <v>1135200</v>
+        <v>1358300</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46073</v>
+        <v>46083</v>
       </c>
       <c r="B166" t="n">
-        <v>1466.387084960938</v>
+        <v>1420.4375</v>
       </c>
       <c r="C166" t="n">
-        <v>1483.769162992887</v>
+        <v>1439.545666025533</v>
       </c>
       <c r="D166" t="n">
-        <v>1445.163422127828</v>
+        <v>1408.13429470469</v>
       </c>
       <c r="E166" t="n">
-        <v>1446.26112218896</v>
+        <v>1414.660080057351</v>
       </c>
       <c r="F166" t="n">
-        <v>1102500</v>
+        <v>1492400</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46076</v>
+        <v>46084</v>
       </c>
       <c r="B167" t="n">
-        <v>1482.751342773438</v>
+        <v>1357.973876953125</v>
       </c>
       <c r="C167" t="n">
-        <v>1489.756062492051</v>
+        <v>1370.506561860358</v>
       </c>
       <c r="D167" t="n">
-        <v>1458.813637629454</v>
+        <v>1326.13351005521</v>
       </c>
       <c r="E167" t="n">
-        <v>1468.193175118705</v>
+        <v>1354.621214432505</v>
       </c>
       <c r="F167" t="n">
-        <v>1284200</v>
+        <v>2012500</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46077</v>
+        <v>46085</v>
       </c>
       <c r="B168" t="n">
-        <v>1494.53564453125</v>
+        <v>1396.320190429688</v>
       </c>
       <c r="C168" t="n">
-        <v>1504.064757548291</v>
+        <v>1402.48677525331</v>
       </c>
       <c r="D168" t="n">
-        <v>1470.71767325709</v>
+        <v>1369.718259466086</v>
       </c>
       <c r="E168" t="n">
-        <v>1496.750776883683</v>
+        <v>1388.098158534372</v>
       </c>
       <c r="F168" t="n">
-        <v>1538900</v>
+        <v>1486700</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46078</v>
+        <v>46086</v>
       </c>
       <c r="B169" t="n">
-        <v>1523.18310546875</v>
+        <v>1365.377685546875</v>
       </c>
       <c r="C169" t="n">
-        <v>1543.847930732333</v>
+        <v>1404.312662108532</v>
       </c>
       <c r="D169" t="n">
-        <v>1513.174935804208</v>
+        <v>1336.530659925031</v>
       </c>
       <c r="E169" t="n">
-        <v>1519.082077495677</v>
+        <v>1378.109885251522</v>
       </c>
       <c r="F169" t="n">
-        <v>1306900</v>
+        <v>1804500</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46079</v>
+        <v>46087</v>
       </c>
       <c r="B170" t="n">
-        <v>1460.609741210938</v>
+        <v>1289.982421875</v>
       </c>
       <c r="C170" t="n">
-        <v>1511.029520043906</v>
+        <v>1335.083860828518</v>
       </c>
       <c r="D170" t="n">
-        <v>1423.480756445574</v>
+        <v>1283.865777192008</v>
       </c>
       <c r="E170" t="n">
-        <v>1509.522801298568</v>
+        <v>1291.040048291999</v>
       </c>
       <c r="F170" t="n">
-        <v>2177900</v>
+        <v>1900100</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46080</v>
+        <v>46090</v>
       </c>
       <c r="B171" t="n">
-        <v>1447.398681640625</v>
+        <v>1354.461669921875</v>
       </c>
       <c r="C171" t="n">
-        <v>1458.534271634737</v>
+        <v>1356.038182605462</v>
       </c>
       <c r="D171" t="n">
-        <v>1421.395418812171</v>
+        <v>1273.328819235332</v>
       </c>
       <c r="E171" t="n">
-        <v>1427.222656904843</v>
+        <v>1281.989955555492</v>
       </c>
       <c r="F171" t="n">
-        <v>1358300</v>
+        <v>1808900</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="B172" t="n">
-        <v>1420.4375</v>
+        <v>1380.385009765625</v>
       </c>
       <c r="C172" t="n">
-        <v>1439.545666025533</v>
+        <v>1404.47241309666</v>
       </c>
       <c r="D172" t="n">
-        <v>1408.13429470469</v>
+        <v>1366.924419934204</v>
       </c>
       <c r="E172" t="n">
-        <v>1414.660080057351</v>
+        <v>1371.594152021409</v>
       </c>
       <c r="F172" t="n">
-        <v>1492400</v>
+        <v>1650900</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46084</v>
+        <v>46092</v>
       </c>
       <c r="B173" t="n">
-        <v>1357.973876953125</v>
+        <v>1383.657836914062</v>
       </c>
       <c r="C173" t="n">
-        <v>1370.506561860358</v>
+        <v>1401.718364286915</v>
       </c>
       <c r="D173" t="n">
-        <v>1326.13351005521</v>
+        <v>1369.009777825666</v>
       </c>
       <c r="E173" t="n">
-        <v>1354.621214432505</v>
+        <v>1380.943672480076</v>
       </c>
       <c r="F173" t="n">
-        <v>2012500</v>
+        <v>1164700</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46085</v>
+        <v>46093</v>
       </c>
       <c r="B174" t="n">
-        <v>1396.320190429688</v>
+        <v>1348.63427734375</v>
       </c>
       <c r="C174" t="n">
-        <v>1402.48677525331</v>
+        <v>1369.548679243302</v>
       </c>
       <c r="D174" t="n">
-        <v>1369.718259466086</v>
+        <v>1330.663519197767</v>
       </c>
       <c r="E174" t="n">
-        <v>1388.098158534372</v>
+        <v>1369.548679243302</v>
       </c>
       <c r="F174" t="n">
-        <v>1486700</v>
+        <v>1780200</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46086</v>
+        <v>46094</v>
       </c>
       <c r="B175" t="n">
-        <v>1365.377685546875</v>
+        <v>1342.757080078125</v>
       </c>
       <c r="C175" t="n">
-        <v>1404.312662108532</v>
+        <v>1383.767602206396</v>
       </c>
       <c r="D175" t="n">
-        <v>1336.530659925031</v>
+        <v>1339.574090983475</v>
       </c>
       <c r="E175" t="n">
-        <v>1378.109885251522</v>
+        <v>1364.559556581493</v>
       </c>
       <c r="F175" t="n">
-        <v>1804500</v>
+        <v>1179000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46087</v>
+        <v>46097</v>
       </c>
       <c r="B176" t="n">
-        <v>1289.982421875</v>
+        <v>1372.562133789062</v>
       </c>
       <c r="C176" t="n">
-        <v>1335.083860828518</v>
+        <v>1387.130289878146</v>
       </c>
       <c r="D176" t="n">
-        <v>1283.865777192008</v>
+        <v>1365.218067141611</v>
       </c>
       <c r="E176" t="n">
-        <v>1291.040048291999</v>
+        <v>1376.513464303597</v>
       </c>
       <c r="F176" t="n">
-        <v>1900100</v>
+        <v>1310400</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46090</v>
+        <v>46098</v>
       </c>
       <c r="B177" t="n">
-        <v>1354.461669921875</v>
+        <v>1386.132446289062</v>
       </c>
       <c r="C177" t="n">
-        <v>1356.038182605462</v>
+        <v>1388.028329718094</v>
       </c>
       <c r="D177" t="n">
-        <v>1273.328819235332</v>
+        <v>1366.325732490273</v>
       </c>
       <c r="E177" t="n">
-        <v>1281.989955555492</v>
+        <v>1382.031418394938</v>
       </c>
       <c r="F177" t="n">
-        <v>1808900</v>
+        <v>1135600</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46091</v>
+        <v>46099</v>
       </c>
       <c r="B178" t="n">
-        <v>1380.385009765625</v>
+        <v>1352.216552734375</v>
       </c>
       <c r="C178" t="n">
-        <v>1404.47241309666</v>
+        <v>1378.279621286256</v>
       </c>
       <c r="D178" t="n">
-        <v>1366.924419934204</v>
+        <v>1351.069034712049</v>
       </c>
       <c r="E178" t="n">
-        <v>1371.594152021409</v>
+        <v>1370.376838481187</v>
       </c>
       <c r="F178" t="n">
-        <v>1650900</v>
+        <v>1391400</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="B179" t="n">
-        <v>1383.657836914062</v>
+        <v>1363.411987304688</v>
       </c>
       <c r="C179" t="n">
-        <v>1401.718364286915</v>
+        <v>1369.468704233296</v>
       </c>
       <c r="D179" t="n">
-        <v>1369.009777825666</v>
+        <v>1307.514062598614</v>
       </c>
       <c r="E179" t="n">
-        <v>1380.943672480076</v>
+        <v>1312.373443631633</v>
       </c>
       <c r="F179" t="n">
-        <v>1164700</v>
+        <v>1619100</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46093</v>
+        <v>46101</v>
       </c>
       <c r="B180" t="n">
-        <v>1348.63427734375</v>
+        <v>1314.379150390625</v>
       </c>
       <c r="C180" t="n">
-        <v>1369.548679243302</v>
+        <v>1367.014185640658</v>
       </c>
       <c r="D180" t="n">
-        <v>1330.663519197767</v>
+        <v>1288.286118033783</v>
       </c>
       <c r="E180" t="n">
-        <v>1369.548679243302</v>
+        <v>1354.301961279114</v>
       </c>
       <c r="F180" t="n">
-        <v>1780200</v>
+        <v>2645100</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46094</v>
+        <v>46104</v>
       </c>
       <c r="B181" t="n">
-        <v>1342.757080078125</v>
+        <v>1366.635009765625</v>
       </c>
       <c r="C181" t="n">
-        <v>1383.767602206396</v>
+        <v>1397.337968317994</v>
       </c>
       <c r="D181" t="n">
-        <v>1339.574090983475</v>
+        <v>1345.171879473351</v>
       </c>
       <c r="E181" t="n">
-        <v>1364.559556581493</v>
+        <v>1356.766549671705</v>
       </c>
       <c r="F181" t="n">
-        <v>1179000</v>
+        <v>1983200</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46097</v>
+        <v>46105</v>
       </c>
       <c r="B182" t="n">
-        <v>1372.562133789062</v>
+        <v>1396.3701171875</v>
       </c>
       <c r="C182" t="n">
-        <v>1387.130289878146</v>
+        <v>1410.199895782793</v>
       </c>
       <c r="D182" t="n">
-        <v>1365.218067141611</v>
+        <v>1345.740710801467</v>
       </c>
       <c r="E182" t="n">
-        <v>1376.513464303597</v>
+        <v>1346.179693389761</v>
       </c>
       <c r="F182" t="n">
-        <v>1310400</v>
+        <v>1801000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46098</v>
+        <v>46106</v>
       </c>
       <c r="B183" t="n">
-        <v>1386.132446289062</v>
+        <v>1390.85205078125</v>
       </c>
       <c r="C183" t="n">
-        <v>1388.028329718094</v>
+        <v>1402.765969251553</v>
       </c>
       <c r="D183" t="n">
-        <v>1366.325732490273</v>
+        <v>1363.711259719741</v>
       </c>
       <c r="E183" t="n">
-        <v>1382.031418394938</v>
+        <v>1391.051566162332</v>
       </c>
       <c r="F183" t="n">
-        <v>1135600</v>
+        <v>1610000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46099</v>
+        <v>46107</v>
       </c>
       <c r="B184" t="n">
-        <v>1352.216552734375</v>
+        <v>1326.602416992188</v>
       </c>
       <c r="C184" t="n">
-        <v>1378.279621286256</v>
+        <v>1356.457251602465</v>
       </c>
       <c r="D184" t="n">
-        <v>1351.069034712049</v>
+        <v>1323.958168182271</v>
       </c>
       <c r="E184" t="n">
-        <v>1370.376838481187</v>
+        <v>1353.852954591787</v>
       </c>
       <c r="F184" t="n">
-        <v>1391400</v>
+        <v>1721100</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46100</v>
+        <v>46108</v>
       </c>
       <c r="B185" t="n">
-        <v>1363.411987304688</v>
+        <v>1299.63134765625</v>
       </c>
       <c r="C185" t="n">
-        <v>1369.468704233296</v>
+        <v>1330.873168627696</v>
       </c>
       <c r="D185" t="n">
-        <v>1307.514062598614</v>
+        <v>1295.69000506859</v>
       </c>
       <c r="E185" t="n">
-        <v>1312.373443631633</v>
+        <v>1315.55664701417</v>
       </c>
       <c r="F185" t="n">
-        <v>1619100</v>
+        <v>1759700</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46101</v>
+        <v>46111</v>
       </c>
       <c r="B186" t="n">
-        <v>1314.379150390625</v>
+        <v>1251.22705078125</v>
       </c>
       <c r="C186" t="n">
-        <v>1367.014185640658</v>
+        <v>1320.036840544383</v>
       </c>
       <c r="D186" t="n">
-        <v>1288.286118033783</v>
+        <v>1245.389824771209</v>
       </c>
       <c r="E186" t="n">
-        <v>1354.301961279114</v>
+        <v>1315.89586079221</v>
       </c>
       <c r="F186" t="n">
-        <v>2645100</v>
+        <v>2144500</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46104</v>
+        <v>46112</v>
       </c>
       <c r="B187" t="n">
-        <v>1366.635009765625</v>
+        <v>1317.951293945312</v>
       </c>
       <c r="C187" t="n">
-        <v>1397.337968317994</v>
+        <v>1319.527928393852</v>
       </c>
       <c r="D187" t="n">
-        <v>1345.171879473351</v>
+        <v>1273.229029784472</v>
       </c>
       <c r="E187" t="n">
-        <v>1356.766549671705</v>
+        <v>1281.530843297226</v>
       </c>
       <c r="F187" t="n">
-        <v>1983200</v>
+        <v>1731500</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="B188" t="n">
-        <v>1396.3701171875</v>
+        <v>1356.796508789062</v>
       </c>
       <c r="C188" t="n">
-        <v>1410.199895782793</v>
+        <v>1382.699891823817</v>
       </c>
       <c r="D188" t="n">
-        <v>1345.740710801467</v>
+        <v>1341.629684838034</v>
       </c>
       <c r="E188" t="n">
-        <v>1346.179693389761</v>
+        <v>1342.707287204718</v>
       </c>
       <c r="F188" t="n">
-        <v>1801000</v>
+        <v>1745000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="B189" t="n">
-        <v>1390.85205078125</v>
+        <v>1314.359130859375</v>
       </c>
       <c r="C189" t="n">
-        <v>1402.765969251553</v>
+        <v>1353.244168083283</v>
       </c>
       <c r="D189" t="n">
-        <v>1363.711259719741</v>
+        <v>1295.350722648515</v>
       </c>
       <c r="E189" t="n">
-        <v>1391.051566162332</v>
+        <v>1302.694667208883</v>
       </c>
       <c r="F189" t="n">
-        <v>1610000</v>
+        <v>1883400</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46107</v>
+        <v>46118</v>
       </c>
       <c r="B190" t="n">
-        <v>1326.602416992188</v>
+        <v>1301.16796875</v>
       </c>
       <c r="C190" t="n">
-        <v>1356.457251602465</v>
+        <v>1317.123109399061</v>
       </c>
       <c r="D190" t="n">
-        <v>1323.958168182271</v>
+        <v>1277.569488679081</v>
       </c>
       <c r="E190" t="n">
-        <v>1353.852954591787</v>
+        <v>1312.243752354548</v>
       </c>
       <c r="F190" t="n">
-        <v>1721100</v>
+        <v>1299200</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="B191" t="n">
-        <v>1299.63134765625</v>
+        <v>1303.602661132812</v>
       </c>
       <c r="C191" t="n">
-        <v>1330.873168627696</v>
+        <v>1306.147152359117</v>
       </c>
       <c r="D191" t="n">
-        <v>1295.69000506859</v>
+        <v>1269.437293874269</v>
       </c>
       <c r="E191" t="n">
-        <v>1315.55664701417</v>
+        <v>1287.62754374197</v>
       </c>
       <c r="F191" t="n">
-        <v>1759700</v>
+        <v>1368900</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46111</v>
+        <v>46120</v>
       </c>
       <c r="B192" t="n">
-        <v>1251.22705078125</v>
+        <v>1417.953002929688</v>
       </c>
       <c r="C192" t="n">
-        <v>1320.036840544383</v>
+        <v>1426.175034874712</v>
       </c>
       <c r="D192" t="n">
-        <v>1245.389824771209</v>
+        <v>1381.213180471424</v>
       </c>
       <c r="E192" t="n">
-        <v>1315.89586079221</v>
+        <v>1417.90306317831</v>
       </c>
       <c r="F192" t="n">
-        <v>2144500</v>
+        <v>2427300</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46112</v>
+        <v>46121</v>
       </c>
       <c r="B193" t="n">
-        <v>1317.951293945312</v>
+        <v>1445.482788085938</v>
       </c>
       <c r="C193" t="n">
-        <v>1319.527928393852</v>
+        <v>1450.382121132025</v>
       </c>
       <c r="D193" t="n">
-        <v>1273.229029784472</v>
+        <v>1409.042361810818</v>
       </c>
       <c r="E193" t="n">
-        <v>1281.530843297226</v>
+        <v>1409.042361810818</v>
       </c>
       <c r="F193" t="n">
-        <v>1731500</v>
+        <v>1579700</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="B194" t="n">
-        <v>1356.796508789062</v>
+        <v>1475.058227539062</v>
       </c>
       <c r="C194" t="n">
-        <v>1382.699891823817</v>
+        <v>1499.225412611157</v>
       </c>
       <c r="D194" t="n">
-        <v>1341.629684838034</v>
+        <v>1470.508107255039</v>
       </c>
       <c r="E194" t="n">
-        <v>1342.707287204718</v>
+        <v>1479.119303681841</v>
       </c>
       <c r="F194" t="n">
-        <v>1745000</v>
+        <v>1519600</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="B195" t="n">
-        <v>1314.359130859375</v>
+        <v>1496.930297851562</v>
       </c>
       <c r="C195" t="n">
-        <v>1353.244168083283</v>
+        <v>1497.52908760796</v>
       </c>
       <c r="D195" t="n">
-        <v>1295.350722648515</v>
+        <v>1457.845745973419</v>
       </c>
       <c r="E195" t="n">
-        <v>1302.694667208883</v>
+        <v>1461.966749599987</v>
       </c>
       <c r="F195" t="n">
-        <v>1883400</v>
+        <v>1709400</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="B196" t="n">
-        <v>1301.16796875</v>
+        <v>1514.990966796875</v>
       </c>
       <c r="C196" t="n">
-        <v>1317.123109399061</v>
+        <v>1528.641083503347</v>
       </c>
       <c r="D196" t="n">
-        <v>1277.569488679081</v>
+        <v>1493.717364783311</v>
       </c>
       <c r="E196" t="n">
-        <v>1312.243752354548</v>
+        <v>1523.063300818684</v>
       </c>
       <c r="F196" t="n">
-        <v>1299200</v>
+        <v>1769200</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="B197" t="n">
-        <v>1303.602661132812</v>
+        <v>1478.54052734375</v>
       </c>
       <c r="C197" t="n">
-        <v>1306.147152359117</v>
+        <v>1482.930961980531</v>
       </c>
       <c r="D197" t="n">
-        <v>1269.437293874269</v>
+        <v>1412.16548704717</v>
       </c>
       <c r="E197" t="n">
-        <v>1287.62754374197</v>
+        <v>1470.318496025898</v>
       </c>
       <c r="F197" t="n">
-        <v>1368900</v>
+        <v>4251700</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46120</v>
+        <v>46128</v>
       </c>
       <c r="B198" t="n">
-        <v>1417.953002929688</v>
+        <v>1407.755126953125</v>
       </c>
       <c r="C198" t="n">
-        <v>1426.175034874712</v>
+        <v>1450.751302281385</v>
       </c>
       <c r="D198" t="n">
-        <v>1381.213180471424</v>
+        <v>1403.434607808129</v>
       </c>
       <c r="E198" t="n">
-        <v>1417.90306317831</v>
+        <v>1449.83326352308</v>
       </c>
       <c r="F198" t="n">
-        <v>2427300</v>
+        <v>2626700</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46121</v>
+        <v>46129</v>
       </c>
       <c r="B199" t="n">
-        <v>1445.482788085938</v>
+        <v>1456.618530273438</v>
       </c>
       <c r="C199" t="n">
-        <v>1450.382121132025</v>
+        <v>1469.270827007611</v>
       </c>
       <c r="D199" t="n">
-        <v>1409.042361810818</v>
+        <v>1442.539174712824</v>
       </c>
       <c r="E199" t="n">
-        <v>1409.042361810818</v>
+        <v>1460.5698607898</v>
       </c>
       <c r="F199" t="n">
-        <v>1579700</v>
+        <v>1876500</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="B200" t="n">
-        <v>1475.058227539062</v>
+        <v>1473.282104492188</v>
       </c>
       <c r="C200" t="n">
-        <v>1499.225412611157</v>
+        <v>1476.076050872263</v>
       </c>
       <c r="D200" t="n">
-        <v>1470.508107255039</v>
+        <v>1448.835499981481</v>
       </c>
       <c r="E200" t="n">
-        <v>1479.119303681841</v>
+        <v>1458.304807657817</v>
       </c>
       <c r="F200" t="n">
-        <v>1519600</v>
+        <v>1091900</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="B201" t="n">
-        <v>1496.930297851562</v>
+        <v>1455.790283203125</v>
       </c>
       <c r="C201" t="n">
-        <v>1497.52908760796</v>
+        <v>1476.944152884416</v>
       </c>
       <c r="D201" t="n">
-        <v>1457.845745973419</v>
+        <v>1443.098034476913</v>
       </c>
       <c r="E201" t="n">
-        <v>1461.966749599987</v>
+        <v>1472.872966905021</v>
       </c>
       <c r="F201" t="n">
-        <v>1709400</v>
+        <v>1274600</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46126</v>
+        <v>46134</v>
       </c>
       <c r="B202" t="n">
-        <v>1514.990966796875</v>
+        <v>1440.513671875</v>
       </c>
       <c r="C202" t="n">
-        <v>1528.641083503347</v>
+        <v>1473.780975427734</v>
       </c>
       <c r="D202" t="n">
-        <v>1493.717364783311</v>
+        <v>1375.29613432228</v>
       </c>
       <c r="E202" t="n">
-        <v>1523.063300818684</v>
+        <v>1473.780975427734</v>
       </c>
       <c r="F202" t="n">
-        <v>1769200</v>
+        <v>2621800</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="B203" t="n">
-        <v>1478.54052734375</v>
+        <v>1414.710083007812</v>
       </c>
       <c r="C203" t="n">
-        <v>1482.930961980531</v>
+        <v>1446.839857324623</v>
       </c>
       <c r="D203" t="n">
-        <v>1412.16548704717</v>
+        <v>1393.187024643978</v>
       </c>
       <c r="E203" t="n">
-        <v>1470.318496025898</v>
+        <v>1435.81389106951</v>
       </c>
       <c r="F203" t="n">
-        <v>4251700</v>
+        <v>1800500</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46128</v>
+        <v>46136</v>
       </c>
       <c r="B204" t="n">
-        <v>1407.755126953125</v>
+        <v>1454.52294921875</v>
       </c>
       <c r="C204" t="n">
-        <v>1450.751302281385</v>
+        <v>1469.44043934131</v>
       </c>
       <c r="D204" t="n">
-        <v>1403.434607808129</v>
+        <v>1438.547832664347</v>
       </c>
       <c r="E204" t="n">
-        <v>1449.83326352308</v>
+        <v>1456.34903875764</v>
       </c>
       <c r="F204" t="n">
-        <v>2626700</v>
+        <v>1751800</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46129</v>
+        <v>46139</v>
       </c>
       <c r="B205" t="n">
-        <v>1456.618530273438</v>
+        <v>1432.43994140625</v>
       </c>
       <c r="C205" t="n">
-        <v>1469.270827007611</v>
+        <v>1458.300048828125</v>
       </c>
       <c r="D205" t="n">
-        <v>1442.539174712824</v>
+        <v>1415.68994140625</v>
       </c>
       <c r="E205" t="n">
-        <v>1460.5698607898</v>
+        <v>1457.839965820312</v>
       </c>
       <c r="F205" t="n">
-        <v>1876500</v>
+        <v>1326200</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46132</v>
+        <v>46140</v>
       </c>
       <c r="B206" t="n">
-        <v>1473.282104492188</v>
+        <v>1384.56005859375</v>
       </c>
       <c r="C206" t="n">
-        <v>1476.076050872263</v>
+        <v>1398.630004882812</v>
       </c>
       <c r="D206" t="n">
-        <v>1448.835499981481</v>
+        <v>1364.81005859375</v>
       </c>
       <c r="E206" t="n">
-        <v>1458.304807657817</v>
+        <v>1389.72998046875</v>
       </c>
       <c r="F206" t="n">
-        <v>1091900</v>
+        <v>1926900</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46133</v>
+        <v>46141</v>
       </c>
       <c r="B207" t="n">
-        <v>1455.790283203125</v>
+        <v>1394.079956054688</v>
       </c>
       <c r="C207" t="n">
-        <v>1476.944152884416</v>
+        <v>1399.699951171875</v>
       </c>
       <c r="D207" t="n">
-        <v>1443.098034476913</v>
+        <v>1374.920043945312</v>
       </c>
       <c r="E207" t="n">
-        <v>1472.872966905021</v>
+        <v>1386.7099609375</v>
       </c>
       <c r="F207" t="n">
-        <v>1274600</v>
+        <v>1256500</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46134</v>
+        <v>46142</v>
       </c>
       <c r="B208" t="n">
-        <v>1440.513671875</v>
+        <v>1438.989990234375</v>
       </c>
       <c r="C208" t="n">
-        <v>1473.780975427734</v>
+        <v>1446.650024414062</v>
       </c>
       <c r="D208" t="n">
-        <v>1375.29613432228</v>
+        <v>1395</v>
       </c>
       <c r="E208" t="n">
-        <v>1473.780975427734</v>
+        <v>1414.339965820312</v>
       </c>
       <c r="F208" t="n">
-        <v>2621800</v>
+        <v>1414400</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46135</v>
+        <v>46143</v>
       </c>
       <c r="B209" t="n">
-        <v>1414.710083007812</v>
+        <v>1427.02001953125</v>
       </c>
       <c r="C209" t="n">
-        <v>1446.839857324623</v>
+        <v>1444.150024414062</v>
       </c>
       <c r="D209" t="n">
-        <v>1393.187024643978</v>
+        <v>1414</v>
       </c>
       <c r="E209" t="n">
-        <v>1435.81389106951</v>
+        <v>1428.2900390625</v>
       </c>
       <c r="F209" t="n">
-        <v>1800500</v>
+        <v>707100</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46136</v>
+        <v>46146</v>
       </c>
       <c r="B210" t="n">
-        <v>1454.52294921875</v>
+        <v>1386.2099609375</v>
       </c>
       <c r="C210" t="n">
-        <v>1469.44043934131</v>
+        <v>1417.069946289062</v>
       </c>
       <c r="D210" t="n">
-        <v>1438.547832664347</v>
+        <v>1366.7900390625</v>
       </c>
       <c r="E210" t="n">
-        <v>1456.34903875764</v>
+        <v>1401.77001953125</v>
       </c>
       <c r="F210" t="n">
-        <v>1751800</v>
+        <v>1755700</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46139</v>
+        <v>46147</v>
       </c>
       <c r="B211" t="n">
-        <v>1432.43994140625</v>
+        <v>1442.920043945312</v>
       </c>
       <c r="C211" t="n">
-        <v>1458.300048828125</v>
+        <v>1454.800048828125</v>
       </c>
       <c r="D211" t="n">
-        <v>1415.68994140625</v>
+        <v>1414.390014648438</v>
       </c>
       <c r="E211" t="n">
-        <v>1457.839965820312</v>
+        <v>1432.420043945312</v>
       </c>
       <c r="F211" t="n">
-        <v>1326200</v>
+        <v>1621400</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="B212" t="n">
-        <v>1384.56005859375</v>
+        <v>1544.739990234375</v>
       </c>
       <c r="C212" t="n">
-        <v>1398.630004882812</v>
+        <v>1545.52001953125</v>
       </c>
       <c r="D212" t="n">
-        <v>1364.81005859375</v>
+        <v>1496</v>
       </c>
       <c r="E212" t="n">
-        <v>1389.72998046875</v>
+        <v>1503.089965820312</v>
       </c>
       <c r="F212" t="n">
-        <v>1926900</v>
+        <v>2312400</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>46141</v>
+        <v>46149</v>
       </c>
       <c r="B213" t="n">
-        <v>1394.079956054688</v>
+        <v>1516.599975585938</v>
       </c>
       <c r="C213" t="n">
-        <v>1399.699951171875</v>
+        <v>1550</v>
       </c>
       <c r="D213" t="n">
-        <v>1374.920043945312</v>
+        <v>1497.81005859375</v>
       </c>
       <c r="E213" t="n">
-        <v>1386.7099609375</v>
+        <v>1548.739990234375</v>
       </c>
       <c r="F213" t="n">
-        <v>1256500</v>
+        <v>1726700</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>46142</v>
+        <v>46150</v>
       </c>
       <c r="B214" t="n">
-        <v>1438.989990234375</v>
+        <v>1592.02001953125</v>
       </c>
       <c r="C214" t="n">
-        <v>1446.650024414062</v>
+        <v>1595.31005859375</v>
       </c>
       <c r="D214" t="n">
-        <v>1395</v>
+        <v>1531.160034179688</v>
       </c>
       <c r="E214" t="n">
-        <v>1414.339965820312</v>
+        <v>1538.530029296875</v>
       </c>
       <c r="F214" t="n">
-        <v>1414400</v>
+        <v>2288300</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>46143</v>
+        <v>46153</v>
       </c>
       <c r="B215" t="n">
-        <v>1427.02001953125</v>
+        <v>1565.81005859375</v>
       </c>
       <c r="C215" t="n">
-        <v>1444.150024414062</v>
+        <v>1567.989990234375</v>
       </c>
       <c r="D215" t="n">
-        <v>1414</v>
+        <v>1521.359985351562</v>
       </c>
       <c r="E215" t="n">
-        <v>1428.2900390625</v>
+        <v>1559.300048828125</v>
       </c>
       <c r="F215" t="n">
-        <v>707100</v>
+        <v>2191300</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="B216" t="n">
-        <v>1386.2099609375</v>
+        <v>1520.93994140625</v>
       </c>
       <c r="C216" t="n">
-        <v>1417.069946289062</v>
+        <v>1535.109985351562</v>
       </c>
       <c r="D216" t="n">
-        <v>1366.7900390625</v>
+        <v>1475</v>
       </c>
       <c r="E216" t="n">
-        <v>1401.77001953125</v>
+        <v>1526.140014648438</v>
       </c>
       <c r="F216" t="n">
-        <v>1755700</v>
+        <v>1846800</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="B217" t="n">
-        <v>1442.920043945312</v>
+        <v>1581.579956054688</v>
       </c>
       <c r="C217" t="n">
-        <v>1454.800048828125</v>
+        <v>1602.599975585938</v>
       </c>
       <c r="D217" t="n">
-        <v>1414.390014648438</v>
+        <v>1521.079956054688</v>
       </c>
       <c r="E217" t="n">
-        <v>1432.420043945312</v>
+        <v>1539.390014648438</v>
       </c>
       <c r="F217" t="n">
-        <v>1621400</v>
+        <v>1691200</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>46148</v>
+        <v>46156</v>
       </c>
       <c r="B218" t="n">
-        <v>1544.739990234375</v>
+        <v>1584.510009765625</v>
       </c>
       <c r="C218" t="n">
-        <v>1545.52001953125</v>
+        <v>1603.489990234375</v>
       </c>
       <c r="D218" t="n">
-        <v>1496</v>
+        <v>1563.280029296875</v>
       </c>
       <c r="E218" t="n">
-        <v>1503.089965820312</v>
+        <v>1573.739990234375</v>
       </c>
       <c r="F218" t="n">
-        <v>2312400</v>
+        <v>1412600</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>46149</v>
+        <v>46157</v>
       </c>
       <c r="B219" t="n">
-        <v>1516.599975585938</v>
+        <v>1501.81005859375</v>
       </c>
       <c r="C219" t="n">
-        <v>1550</v>
+        <v>1527.25</v>
       </c>
       <c r="D219" t="n">
-        <v>1497.81005859375</v>
+        <v>1486.640014648438</v>
       </c>
       <c r="E219" t="n">
-        <v>1548.739990234375</v>
+        <v>1511.739990234375</v>
       </c>
       <c r="F219" t="n">
-        <v>1726700</v>
+        <v>1807400</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>46150</v>
+        <v>46160</v>
       </c>
       <c r="B220" t="n">
-        <v>1592.02001953125</v>
+        <v>1472.390014648438</v>
       </c>
       <c r="C220" t="n">
-        <v>1595.31005859375</v>
+        <v>1522.489990234375</v>
       </c>
       <c r="D220" t="n">
-        <v>1531.160034179688</v>
+        <v>1453.339965820312</v>
       </c>
       <c r="E220" t="n">
-        <v>1538.530029296875</v>
+        <v>1521.25</v>
       </c>
       <c r="F220" t="n">
-        <v>2288300</v>
+        <v>1664400</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="B221" t="n">
-        <v>1565.81005859375</v>
+        <v>1459.43994140625</v>
       </c>
       <c r="C221" t="n">
-        <v>1567.989990234375</v>
+        <v>1485.760009765625</v>
       </c>
       <c r="D221" t="n">
-        <v>1521.359985351562</v>
+        <v>1441.31005859375</v>
       </c>
       <c r="E221" t="n">
-        <v>1559.300048828125</v>
+        <v>1449.930053710938</v>
       </c>
       <c r="F221" t="n">
-        <v>2191300</v>
+        <v>1395400</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>46154</v>
+        <v>46162</v>
       </c>
       <c r="B222" t="n">
-        <v>1520.93994140625</v>
+        <v>1550.130004882812</v>
       </c>
       <c r="C222" t="n">
-        <v>1535.109985351562</v>
+        <v>1555.800048828125</v>
       </c>
       <c r="D222" t="n">
-        <v>1475</v>
+        <v>1492.319946289062</v>
       </c>
       <c r="E222" t="n">
-        <v>1526.140014648438</v>
+        <v>1502.380004882812</v>
       </c>
       <c r="F222" t="n">
-        <v>1846800</v>
+        <v>1744500</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>46155</v>
+        <v>46163</v>
       </c>
       <c r="B223" t="n">
-        <v>1581.579956054688</v>
+        <v>1592</v>
       </c>
       <c r="C223" t="n">
-        <v>1602.599975585938</v>
+        <v>1601.7900390625</v>
       </c>
       <c r="D223" t="n">
-        <v>1521.079956054688</v>
+        <v>1545.93994140625</v>
       </c>
       <c r="E223" t="n">
-        <v>1539.390014648438</v>
+        <v>1548.680053710938</v>
       </c>
       <c r="F223" t="n">
-        <v>1691200</v>
+        <v>1358400</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>46156</v>
+        <v>46164</v>
       </c>
       <c r="B224" t="n">
-        <v>1584.510009765625</v>
+        <v>1632.900024414062</v>
       </c>
       <c r="C224" t="n">
-        <v>1603.489990234375</v>
+        <v>1653.530029296875</v>
       </c>
       <c r="D224" t="n">
-        <v>1563.280029296875</v>
+        <v>1615.849975585938</v>
       </c>
       <c r="E224" t="n">
-        <v>1573.739990234375</v>
+        <v>1620.030029296875</v>
       </c>
       <c r="F224" t="n">
-        <v>1412600</v>
+        <v>1666700</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>46157</v>
+        <v>46168</v>
       </c>
       <c r="B225" t="n">
-        <v>1501.81005859375</v>
+        <v>1632.030029296875</v>
       </c>
       <c r="C225" t="n">
-        <v>1527.25</v>
+        <v>1648.010009765625</v>
       </c>
       <c r="D225" t="n">
-        <v>1486.640014648438</v>
+        <v>1604.25</v>
       </c>
       <c r="E225" t="n">
-        <v>1511.739990234375</v>
+        <v>1641.849975585938</v>
       </c>
       <c r="F225" t="n">
-        <v>1807400</v>
+        <v>1651000</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="B226" t="n">
-        <v>1472.390014648438</v>
+        <v>1597.869995117188</v>
       </c>
       <c r="C226" t="n">
-        <v>1522.489990234375</v>
+        <v>1639.130004882812</v>
       </c>
       <c r="D226" t="n">
-        <v>1453.339965820312</v>
+        <v>1583</v>
       </c>
       <c r="E226" t="n">
-        <v>1521.25</v>
+        <v>1637.349975585938</v>
       </c>
       <c r="F226" t="n">
-        <v>1664400</v>
+        <v>1361600</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>46161</v>
+        <v>46170</v>
       </c>
       <c r="B227" t="n">
-        <v>1459.43994140625</v>
+        <v>1605.77001953125</v>
       </c>
       <c r="C227" t="n">
-        <v>1485.760009765625</v>
+        <v>1627.530029296875</v>
       </c>
       <c r="D227" t="n">
-        <v>1441.31005859375</v>
+        <v>1580</v>
       </c>
       <c r="E227" t="n">
-        <v>1449.930053710938</v>
+        <v>1617.089965820312</v>
       </c>
       <c r="F227" t="n">
-        <v>1395400</v>
+        <v>971600</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>46162</v>
+        <v>46171</v>
       </c>
       <c r="B228" t="n">
-        <v>1550.130004882812</v>
+        <v>1612.760009765625</v>
       </c>
       <c r="C228" t="n">
-        <v>1555.800048828125</v>
+        <v>1654.199951171875</v>
       </c>
       <c r="D228" t="n">
-        <v>1492.319946289062</v>
+        <v>1604.859985351562</v>
       </c>
       <c r="E228" t="n">
-        <v>1502.380004882812</v>
+        <v>1633.469970703125</v>
       </c>
       <c r="F228" t="n">
-        <v>1744500</v>
+        <v>1069400</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>46163</v>
+        <v>46174</v>
       </c>
       <c r="B229" t="n">
-        <v>1592</v>
+        <v>1628.569946289062</v>
       </c>
       <c r="C229" t="n">
-        <v>1601.7900390625</v>
+        <v>1646.530029296875</v>
       </c>
       <c r="D229" t="n">
-        <v>1545.93994140625</v>
+        <v>1585.609985351562</v>
       </c>
       <c r="E229" t="n">
-        <v>1548.680053710938</v>
+        <v>1594.469970703125</v>
       </c>
       <c r="F229" t="n">
-        <v>1358400</v>
+        <v>1058900</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>46164</v>
+        <v>46175</v>
       </c>
       <c r="B230" t="n">
-        <v>1632.900024414062</v>
+        <v>1705.369995117188</v>
       </c>
       <c r="C230" t="n">
-        <v>1653.530029296875</v>
+        <v>1708.319946289062</v>
       </c>
       <c r="D230" t="n">
-        <v>1615.849975585938</v>
+        <v>1647.589965820312</v>
       </c>
       <c r="E230" t="n">
-        <v>1620.030029296875</v>
+        <v>1659.68994140625</v>
       </c>
       <c r="F230" t="n">
-        <v>1666700</v>
+        <v>1484000</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>46168</v>
+        <v>46176</v>
       </c>
       <c r="B231" t="n">
-        <v>1632.030029296875</v>
+        <v>1726.359985351562</v>
       </c>
       <c r="C231" t="n">
-        <v>1648.010009765625</v>
+        <v>1743.27001953125</v>
       </c>
       <c r="D231" t="n">
-        <v>1604.25</v>
+        <v>1690</v>
       </c>
       <c r="E231" t="n">
-        <v>1641.849975585938</v>
+        <v>1709.31005859375</v>
       </c>
       <c r="F231" t="n">
-        <v>1651000</v>
+        <v>1826900</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>46169</v>
+        <v>46177</v>
       </c>
       <c r="B232" t="n">
-        <v>1597.869995117188</v>
+        <v>1757.469970703125</v>
       </c>
       <c r="C232" t="n">
-        <v>1639.130004882812</v>
+        <v>1779.2900390625</v>
       </c>
       <c r="D232" t="n">
-        <v>1583</v>
+        <v>1672.430053710938</v>
       </c>
       <c r="E232" t="n">
-        <v>1637.349975585938</v>
+        <v>1679.800048828125</v>
       </c>
       <c r="F232" t="n">
-        <v>1361600</v>
+        <v>2248200</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>46170</v>
+        <v>46178</v>
       </c>
       <c r="B233" t="n">
-        <v>1605.77001953125</v>
+        <v>1641.739990234375</v>
       </c>
       <c r="C233" t="n">
-        <v>1627.530029296875</v>
+        <v>1705.47998046875</v>
       </c>
       <c r="D233" t="n">
-        <v>1580</v>
+        <v>1638.380004882812</v>
       </c>
       <c r="E233" t="n">
-        <v>1617.089965820312</v>
+        <v>1685.359985351562</v>
       </c>
       <c r="F233" t="n">
-        <v>971600</v>
+        <v>2744600</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>46171</v>
+        <v>46181</v>
       </c>
       <c r="B234" t="n">
-        <v>1612.760009765625</v>
+        <v>1749.0400390625</v>
       </c>
       <c r="C234" t="n">
-        <v>1654.199951171875</v>
+        <v>1769.489990234375</v>
       </c>
       <c r="D234" t="n">
-        <v>1604.859985351562</v>
+        <v>1719.02001953125</v>
       </c>
       <c r="E234" t="n">
-        <v>1633.469970703125</v>
+        <v>1732.7900390625</v>
       </c>
       <c r="F234" t="n">
-        <v>1069400</v>
+        <v>2062100</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="B235" t="n">
-        <v>1628.569946289062</v>
+        <v>1777.77001953125</v>
       </c>
       <c r="C235" t="n">
-        <v>1646.530029296875</v>
+        <v>1831.109985351562</v>
       </c>
       <c r="D235" t="n">
-        <v>1585.609985351562</v>
+        <v>1676.280029296875</v>
       </c>
       <c r="E235" t="n">
-        <v>1594.469970703125</v>
+        <v>1776.619995117188</v>
       </c>
       <c r="F235" t="n">
-        <v>1058900</v>
+        <v>3151400</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>46175</v>
+        <v>46183</v>
       </c>
       <c r="B236" t="n">
-        <v>1705.369995117188</v>
+        <v>1734.18994140625</v>
       </c>
       <c r="C236" t="n">
-        <v>1708.319946289062</v>
+        <v>1812</v>
       </c>
       <c r="D236" t="n">
-        <v>1647.589965820312</v>
+        <v>1723.2099609375</v>
       </c>
       <c r="E236" t="n">
-        <v>1659.68994140625</v>
+        <v>1746.4599609375</v>
       </c>
       <c r="F236" t="n">
-        <v>1484000</v>
+        <v>2586400</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>46176</v>
+        <v>46184</v>
       </c>
       <c r="B237" t="n">
-        <v>1726.359985351562</v>
+        <v>1899.47998046875</v>
       </c>
       <c r="C237" t="n">
-        <v>1743.27001953125</v>
+        <v>1903.5</v>
       </c>
       <c r="D237" t="n">
-        <v>1690</v>
+        <v>1775.099975585938</v>
       </c>
       <c r="E237" t="n">
-        <v>1709.31005859375</v>
+        <v>1780</v>
       </c>
       <c r="F237" t="n">
-        <v>1826900</v>
+        <v>2965600</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>46177</v>
+        <v>46185</v>
       </c>
       <c r="B238" t="n">
-        <v>1757.469970703125</v>
+        <v>1863.550048828125</v>
       </c>
       <c r="C238" t="n">
-        <v>1779.2900390625</v>
+        <v>1892.800048828125</v>
       </c>
       <c r="D238" t="n">
-        <v>1672.430053710938</v>
+        <v>1839</v>
       </c>
       <c r="E238" t="n">
-        <v>1679.800048828125</v>
+        <v>1847.619995117188</v>
       </c>
       <c r="F238" t="n">
-        <v>2248200</v>
+        <v>2529600</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>46178</v>
+        <v>46188</v>
       </c>
       <c r="B239" t="n">
-        <v>1641.739990234375</v>
+        <v>1892.660034179688</v>
       </c>
       <c r="C239" t="n">
-        <v>1705.47998046875</v>
+        <v>1913.699951171875</v>
       </c>
       <c r="D239" t="n">
-        <v>1638.380004882812</v>
+        <v>1865</v>
       </c>
       <c r="E239" t="n">
-        <v>1685.359985351562</v>
+        <v>1894.5400390625</v>
       </c>
       <c r="F239" t="n">
-        <v>2744600</v>
+        <v>2339100</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46181</v>
+        <v>46189</v>
       </c>
       <c r="B240" t="n">
-        <v>1749.0400390625</v>
+        <v>1803.890014648438</v>
       </c>
       <c r="C240" t="n">
-        <v>1769.489990234375</v>
+        <v>1881.160034179688</v>
       </c>
       <c r="D240" t="n">
-        <v>1719.02001953125</v>
+        <v>1802.609985351562</v>
       </c>
       <c r="E240" t="n">
-        <v>1732.7900390625</v>
+        <v>1872.010009765625</v>
       </c>
       <c r="F240" t="n">
-        <v>2062100</v>
+        <v>1797600</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46182</v>
+        <v>46190</v>
       </c>
       <c r="B241" t="n">
-        <v>1777.77001953125</v>
+        <v>1867.829956054688</v>
       </c>
       <c r="C241" t="n">
-        <v>1831.109985351562</v>
+        <v>1938.489990234375</v>
       </c>
       <c r="D241" t="n">
-        <v>1676.280029296875</v>
+        <v>1865.319946289062</v>
       </c>
       <c r="E241" t="n">
-        <v>1776.619995117188</v>
+        <v>1897.199951171875</v>
       </c>
       <c r="F241" t="n">
-        <v>3151400</v>
+        <v>2322900</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>46183</v>
+        <v>46191</v>
       </c>
       <c r="B242" t="n">
-        <v>1734.18994140625</v>
+        <v>1929.680053710938</v>
       </c>
       <c r="C242" t="n">
-        <v>1812</v>
+        <v>1942.869995117188</v>
       </c>
       <c r="D242" t="n">
-        <v>1723.2099609375</v>
+        <v>1909.530029296875</v>
       </c>
       <c r="E242" t="n">
-        <v>1746.4599609375</v>
+        <v>1924.180053710938</v>
       </c>
       <c r="F242" t="n">
-        <v>2586400</v>
+        <v>2406100</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>46184</v>
+        <v>46195</v>
       </c>
       <c r="B243" t="n">
-        <v>1899.47998046875</v>
+        <v>1929.25</v>
       </c>
       <c r="C243" t="n">
-        <v>1903.5</v>
+        <v>1959.0400390625</v>
       </c>
       <c r="D243" t="n">
-        <v>1775.099975585938</v>
+        <v>1886.43994140625</v>
       </c>
       <c r="E243" t="n">
-        <v>1780</v>
+        <v>1953.52001953125</v>
       </c>
       <c r="F243" t="n">
-        <v>2965600</v>
+        <v>1793300</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>46185</v>
+        <v>46196</v>
       </c>
       <c r="B244" t="n">
-        <v>1863.550048828125</v>
+        <v>1778.4599609375</v>
       </c>
       <c r="C244" t="n">
-        <v>1892.800048828125</v>
+        <v>1812.949951171875</v>
       </c>
       <c r="D244" t="n">
-        <v>1839</v>
+        <v>1755.969970703125</v>
       </c>
       <c r="E244" t="n">
-        <v>1847.619995117188</v>
+        <v>1777.699951171875</v>
       </c>
       <c r="F244" t="n">
-        <v>2529600</v>
+        <v>2415700</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>46188</v>
+        <v>46197</v>
       </c>
       <c r="B245" t="n">
-        <v>1892.660034179688</v>
+        <v>1762.77001953125</v>
       </c>
       <c r="C245" t="n">
-        <v>1913.699951171875</v>
+        <v>1779.650024414062</v>
       </c>
       <c r="D245" t="n">
-        <v>1865</v>
+        <v>1730.2900390625</v>
       </c>
       <c r="E245" t="n">
-        <v>1894.5400390625</v>
+        <v>1750.420043945312</v>
       </c>
       <c r="F245" t="n">
-        <v>2339100</v>
+        <v>2028200</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>46189</v>
+        <v>46198</v>
       </c>
       <c r="B246" t="n">
-        <v>1803.890014648438</v>
+        <v>1841.180053710938</v>
       </c>
       <c r="C246" t="n">
-        <v>1881.160034179688</v>
+        <v>1855.910034179688</v>
       </c>
       <c r="D246" t="n">
-        <v>1802.609985351562</v>
+        <v>1777.0400390625</v>
       </c>
       <c r="E246" t="n">
-        <v>1872.010009765625</v>
+        <v>1855.5</v>
       </c>
       <c r="F246" t="n">
-        <v>1797600</v>
+        <v>2197000</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>46190</v>
+        <v>46199</v>
       </c>
       <c r="B247" t="n">
-        <v>1867.829956054688</v>
+        <v>1794.619995117188</v>
       </c>
       <c r="C247" t="n">
-        <v>1938.489990234375</v>
+        <v>1809</v>
       </c>
       <c r="D247" t="n">
-        <v>1865.319946289062</v>
+        <v>1767.640014648438</v>
       </c>
       <c r="E247" t="n">
-        <v>1897.199951171875</v>
+        <v>1781.660034179688</v>
       </c>
       <c r="F247" t="n">
-        <v>2322900</v>
+        <v>2840000</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>46191</v>
+        <v>46202</v>
       </c>
       <c r="B248" t="n">
-        <v>1929.680053710938</v>
+        <v>1883.109985351562</v>
       </c>
       <c r="C248" t="n">
-        <v>1942.869995117188</v>
+        <v>1886.119995117188</v>
       </c>
       <c r="D248" t="n">
-        <v>1909.530029296875</v>
+        <v>1772.52001953125</v>
       </c>
       <c r="E248" t="n">
-        <v>1924.180053710938</v>
+        <v>1798.949951171875</v>
       </c>
       <c r="F248" t="n">
-        <v>2406100</v>
+        <v>1760500</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B249" t="n">
-        <v>1929.25</v>
+        <v>1989.43994140625</v>
       </c>
       <c r="C249" t="n">
-        <v>1959.0400390625</v>
+        <v>1999.9599609375</v>
       </c>
       <c r="D249" t="n">
-        <v>1886.43994140625</v>
+        <v>1913.880004882812</v>
       </c>
       <c r="E249" t="n">
-        <v>1953.52001953125</v>
+        <v>1915.5</v>
       </c>
       <c r="F249" t="n">
-        <v>1793300</v>
+        <v>2712600</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>46196</v>
+        <v>46204</v>
       </c>
       <c r="B250" t="n">
-        <v>1778.4599609375</v>
+        <v>1843.0400390625</v>
       </c>
       <c r="C250" t="n">
-        <v>1812.949951171875</v>
+        <v>1943</v>
       </c>
       <c r="D250" t="n">
-        <v>1755.969970703125</v>
+        <v>1832.630004882812</v>
       </c>
       <c r="E250" t="n">
-        <v>1777.699951171875</v>
+        <v>1916.280029296875</v>
       </c>
       <c r="F250" t="n">
-        <v>2415700</v>
+        <v>2584700</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>46197</v>
+        <v>46205</v>
       </c>
       <c r="B251" t="n">
-        <v>1762.77001953125</v>
+        <v>1769.319946289062</v>
       </c>
       <c r="C251" t="n">
-        <v>1779.650024414062</v>
+        <v>1858.400024414062</v>
       </c>
       <c r="D251" t="n">
-        <v>1730.2900390625</v>
+        <v>1748.02001953125</v>
       </c>
       <c r="E251" t="n">
-        <v>1750.420043945312</v>
+        <v>1843.97998046875</v>
       </c>
       <c r="F251" t="n">
-        <v>2028200</v>
+        <v>2699100</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>46198</v>
+        <v>46209</v>
       </c>
       <c r="B252" t="n">
-        <v>1841.180053710938</v>
+        <v>1825.069946289062</v>
       </c>
       <c r="C252" t="n">
-        <v>1855.910034179688</v>
+        <v>1868.599975585938</v>
       </c>
       <c r="D252" t="n">
-        <v>1777.0400390625</v>
+        <v>1813.329956054688</v>
       </c>
       <c r="E252" t="n">
-        <v>1855.5</v>
+        <v>1829.64501953125</v>
       </c>
       <c r="F252" t="n">
-        <v>2166484</v>
+        <v>1894429</v>
       </c>
     </row>
   </sheetData>
